--- a/docs/xlsx/jobs-2026-09-17.xlsx
+++ b/docs/xlsx/jobs-2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="560">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1669 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Chapter Director</t>
+  </si>
+  <si>
+    <t>Sierra Club - Oregon Chapter</t>
+  </si>
+  <si>
+    <t>Oregon (Portland preferred), OR</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$125,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-chapter-director-oregon-portland-preferred-oregon/3557049422</t>
+  </si>
+  <si>
+    <t>Communications Production Designer</t>
+  </si>
+  <si>
+    <t>Vermont Center for Ecostudies</t>
+  </si>
+  <si>
+    <t>White River Junction, VT</t>
+  </si>
+  <si>
+    <t>$45,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-communications-production-designer-white-river-junction-vermont/9775082609</t>
+  </si>
+  <si>
+    <t>Development and Administrative Assistant</t>
+  </si>
+  <si>
+    <t>River Alliance of Wisconsin and Midwest Environmental Advocates</t>
+  </si>
+  <si>
+    <t>Madison, WI</t>
+  </si>
+  <si>
+    <t>$20 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-and-administrative-assistant-madison-wisconsin/1866801078</t>
+  </si>
+  <si>
+    <t>Director of Agricultural Programs</t>
+  </si>
+  <si>
+    <t>Resource Conservation District of Greater San Diego County</t>
+  </si>
+  <si>
+    <t>Lakeside (San Diego County), CA</t>
+  </si>
+  <si>
+    <t>$42.84 - $50.55 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-agricultural-programs-lakeside-san-diego-county-california/1161238370</t>
+  </si>
+  <si>
+    <t>Environmental Designer</t>
+  </si>
+  <si>
+    <t>Resource Conservation District of the Santa Monica Mountains</t>
+  </si>
+  <si>
+    <t>Calabasas, CA</t>
+  </si>
+  <si>
+    <t>$36 - $42 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-designer-calabasas-california/2838806532</t>
+  </si>
+  <si>
+    <t>Forestry Specialist - Inspections</t>
+  </si>
+  <si>
+    <t>The Woodlands Township</t>
+  </si>
+  <si>
+    <t>The Woodlands, TX</t>
+  </si>
+  <si>
+    <t>$25.93 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-specialist---inspections-the-woodlands-texas/2397743420</t>
+  </si>
+  <si>
+    <t>Hellbender Private Lands Biologist</t>
+  </si>
+  <si>
+    <t>University of Georgia</t>
+  </si>
+  <si>
+    <t>Lebanon, KY</t>
+  </si>
+  <si>
+    <t>$53,060 per year</t>
+  </si>
+  <si>
+    <t>wildlife-admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hellbender-private-lands-biologist-lebanon-kentucky/8089767684</t>
+  </si>
+  <si>
+    <t>IT Specialist</t>
+  </si>
+  <si>
+    <t>Pheasants Forever, Inc., and Quail Forever</t>
+  </si>
+  <si>
+    <t>St Paul, MN</t>
+  </si>
+  <si>
+    <t>$50,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-it-specialist-st-paul-minnesota/4445721638</t>
+  </si>
+  <si>
+    <t>Natural Resources &amp; Conservation Manager</t>
+  </si>
+  <si>
+    <t>San Dieguito River Valley Regional Open Space Park Joint Powers Authority</t>
+  </si>
+  <si>
+    <t>Escondido, CA</t>
+  </si>
+  <si>
+    <t>$30.77 - $42.31 per hour</t>
+  </si>
+  <si>
+    <t>ecology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources--conservation-manager-escondido-california/8343636228</t>
+  </si>
+  <si>
+    <t>Operations Manager</t>
+  </si>
+  <si>
+    <t>MidCoast Watersheds Council</t>
+  </si>
+  <si>
+    <t>Newport, OR</t>
+  </si>
+  <si>
+    <t>$31 - $35 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-manager-newport-oregon/5686351013</t>
+  </si>
+  <si>
+    <t>OPS Fisheries &amp; Wildlife Biological Scientist II</t>
+  </si>
+  <si>
+    <t>FWC</t>
+  </si>
+  <si>
+    <t>Eastpoint, FL</t>
+  </si>
+  <si>
+    <t>$19 per hour</t>
+  </si>
+  <si>
+    <t>fisheries-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ops-fisheries--wildlife-biological-scientist-ii-eastpoint-florida/8941147269</t>
+  </si>
+  <si>
+    <t>Prescribed Fire Ecology Technician</t>
+  </si>
+  <si>
+    <t>Georgia Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Ceylon Wildlife Management Area, GA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$14 - $17 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-prescribed-fire-ecology-technician-ceylon-wildlife-management-area-georgia/1428209633</t>
+  </si>
+  <si>
+    <t>Program Co-ordinator, Puerto Rico</t>
+  </si>
+  <si>
+    <t>World Parrot Trust</t>
+  </si>
+  <si>
+    <t>Puerto Rico, US</t>
+  </si>
+  <si>
+    <t>$60,000 per year</t>
+  </si>
+  <si>
+    <t>botany-forestry-general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-co-ordinator-puerto-rico-puerto-rico-us-territories/1434392502</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>New York State Education Department/NYS Museum</t>
+  </si>
+  <si>
+    <t>Cambridge, NY</t>
+  </si>
+  <si>
+    <t>$71,019 per year</t>
+  </si>
+  <si>
+    <t>ecology-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-project-coordinator-cambridge-new-york/7370878663</t>
+  </si>
+  <si>
+    <t>Research Assistant</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M University- Kingsville</t>
+  </si>
+  <si>
+    <t>Alpine, TX</t>
+  </si>
+  <si>
+    <t>Commensurate</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-assistant-alpine-texas/8080031650</t>
+  </si>
+  <si>
+    <t>Senior Commercial Manager, Canada</t>
+  </si>
+  <si>
+    <t>Marine Stewardship Council</t>
+  </si>
+  <si>
+    <t>Toronto, Ontario, Canada</t>
+  </si>
+  <si>
+    <t>Competitive</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-commercial-manager-canada-toronto-ontario-canada/8517754469</t>
+  </si>
+  <si>
+    <t>Senior Conservation Project Manager</t>
+  </si>
+  <si>
+    <t>Upper Valley Land Trust</t>
+  </si>
+  <si>
+    <t>Hanover, NH</t>
+  </si>
+  <si>
+    <t>$60,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-conservation-project-manager-hanover-new-hampshire/8690920638</t>
+  </si>
+  <si>
+    <t>Senior Groundwater Pumping Data Specialist</t>
+  </si>
+  <si>
+    <t>California State Water Resources Control Board</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$11,437 - $14,315 per month</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-groundwater-pumping-data-specialist-sacramento-california/7825081711</t>
+  </si>
+  <si>
+    <t>Senior Regional Wildlife Biologist</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Anderson, CA</t>
+  </si>
+  <si>
+    <t>$95,000 - $140,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-regional-wildlife-biologist-anderson-california/2182958456</t>
+  </si>
+  <si>
+    <t>Senior Stormwater Inspector</t>
+  </si>
+  <si>
+    <t>City of Raleigh Stormwater Management</t>
+  </si>
+  <si>
+    <t>Raleigh, NC</t>
+  </si>
+  <si>
+    <t>$63,000 - $78,700 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-stormwater-inspector-raleigh-north-carolina/7339570830</t>
+  </si>
+  <si>
+    <t>Vice President for Ocean Conservation</t>
+  </si>
+  <si>
+    <t>Conservation Law Foundation</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>$150,000 - $180,000 per year</t>
+  </si>
+  <si>
+    <t>marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-for-ocean-conservation-boston-massachusetts/9535321216</t>
+  </si>
+  <si>
+    <t>Wildland Fire Cache Truck Driver</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Tumwater, WA</t>
+  </si>
+  <si>
+    <t>$59,760 - $69,348 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-cache-truck-driver-tumwater-washington/5545652646</t>
+  </si>
+  <si>
+    <t>Wildland Fire Cost Analyst</t>
+  </si>
+  <si>
+    <t>Enumclaw, WA</t>
+  </si>
+  <si>
+    <t>$56,904 - $76,536 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-cost-analyst-enumclaw-washington/1752210095</t>
+  </si>
+  <si>
+    <t>Wildland Fire Hand Crew Squad Boss</t>
+  </si>
+  <si>
+    <t>Dallesport, WA</t>
+  </si>
+  <si>
+    <t>$45,924 - $61,332 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-hand-crew-squad-boss-dallesport-washington/3637191216</t>
+  </si>
+  <si>
+    <t>Wildland Fire Squad Boss</t>
+  </si>
+  <si>
+    <t>East Wenatchee, WA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-squad-boss-east-wenatchee-washington/7697353654</t>
+  </si>
+  <si>
+    <t>Wildlife Specialist</t>
+  </si>
+  <si>
+    <t>USDA Wildlife Services</t>
+  </si>
+  <si>
+    <t>Homestead, FL</t>
+  </si>
+  <si>
+    <t>$40,632 - $58,879 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-specialist-homestead-florida/9405297212</t>
+  </si>
+  <si>
+    <t>Access to Justice Technology &amp; Program Coordinator</t>
+  </si>
+  <si>
+    <t>Louisiana State Bar Association's Access to Justice Program</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/71a67b2793c74bfea0ad44f357d87db2-access-to-justice-technology-program-coordinator-louisiana-state-bar-associations-access-to-justice-program-new-orleans</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Sherman Street Church</t>
+  </si>
+  <si>
+    <t>Grand Rapids, Michigan</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00/hour</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ef628b37c9444883829512800387c515-administrative-assistant-sherman-street-church-grand-rapids</t>
+  </si>
+  <si>
+    <t>National Council of Jewish Women, NY Section</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Poverty, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2558fe5570924e0982ebfb5ee6b5cb22-administrative-assistant-national-council-of-jewish-women-ny-section-new-york</t>
+  </si>
+  <si>
+    <t>ADMNINISTRADOR/A SANTUARIO, AMAZONAS BOLIVIANO</t>
+  </si>
+  <si>
+    <t>Comunidad Inti Wara Yassi (CIWY)</t>
+  </si>
+  <si>
+    <t>Santa Cruz, Santa Cruz, BO</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 200.00 - 300.00/month</t>
+  </si>
+  <si>
+    <t>Environment, Animals, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d434ca7b8e914b13af3061c80a827352-admninistradora-santuario-amazonas-boliviano-comunidad-inti-wara-yassi-ciwy-santa-cruz</t>
+  </si>
+  <si>
+    <t>Aftercare Associate</t>
+  </si>
+  <si>
+    <t>ACE (Association of Community Employment Programs for the Homeless, Inc.)</t>
+  </si>
+  <si>
+    <t>Queens County, New York</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b85e597bd5c494fba4cdab020f4d444-aftercare-associate-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
+  </si>
+  <si>
+    <t>Annual Giving &amp; Grants Manager</t>
+  </si>
+  <si>
+    <t>Educated Choices Program</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Animals, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21dbc1f8fe014449abb6e542151862ec-annual-giving-grants-manager-educated-choices-program-lawrenceville</t>
+  </si>
+  <si>
+    <t>Assistant Director, Grants and Administration</t>
+  </si>
+  <si>
+    <t>Columbia University</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Research Social Science, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d066a871fe354033b924587d5cfa2f68-assistant-director-grants-and-administration-columbia-university-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Learning Director</t>
+  </si>
+  <si>
+    <t>Upstander Project</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61013c26aa9c443c97a04d3defa123df-assistant-learning-director-upstander-project-boston</t>
+  </si>
+  <si>
+    <t>Associate General Counsel</t>
+  </si>
+  <si>
+    <t>Meals on Wheels America</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f03d9eb0bf3a4191af5bfea285f8c0b3-associate-general-counsel-meals-on-wheels-america-arlington</t>
+  </si>
+  <si>
+    <t>Atlanta Science Festival Coordinator</t>
+  </si>
+  <si>
+    <t>Science ATL</t>
+  </si>
+  <si>
+    <t>Decatur, Georgia</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a952117586641afab46a7c1ac92f043-atlanta-science-festival-coordinator-science-atl-decatur</t>
+  </si>
+  <si>
+    <t>Beyond TE Youth Program Manager</t>
+  </si>
+  <si>
+    <t>Center for Teen Empowerment</t>
+  </si>
+  <si>
+    <t>Somerville, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8e9cbd0afd3b44a6986dae2a3edc5caa-beyond-te-youth-program-manager-center-for-teen-empowerment-somerville</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>Job Workplace, Housing Homelessness, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/575699ee9a1f46ba9dea2243f41b50fd-case-manager-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
+  </si>
+  <si>
+    <t>Case Manager &amp; Vocational ESL Instructor</t>
+  </si>
+  <si>
+    <t>Substance Abuse Addiction, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/422f4dcb56a9439b88d231e319293fbc-case-manager-vocational-esl-instructor-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
+  </si>
+  <si>
+    <t>Case Manager for Supportive Housing</t>
+  </si>
+  <si>
+    <t>Community Counseling and Mediation</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd6a834b0de04c348e85034a94f7e0d2-case-manager-for-supportive-housing-community-counseling-and-mediation-brooklyn</t>
+  </si>
+  <si>
+    <t>Chief Development Officer</t>
+  </si>
+  <si>
+    <t>Covenant House Greater Washington</t>
+  </si>
+  <si>
+    <t>Washington, Washington DC</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/843ba5f820a54344a082c228de287741-chief-development-officer-covenant-house-greater-washington-washington</t>
+  </si>
+  <si>
+    <t>Child Trauma Counselor CTRT</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>USD 29.70 - 30.80/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc20e4c13e604dbba792e276ca0e66a4-child-trauma-counselor-ctrt-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>Church Business &amp; Operations Manager</t>
+  </si>
+  <si>
+    <t>United Church in Walpole</t>
+  </si>
+  <si>
+    <t>Walpole, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 44200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74293dc02f6c4da3bb31b380f563ff65-church-business-operations-manager-united-church-in-walpole-walpole</t>
+  </si>
+  <si>
+    <t>Client Reception and Intake Associate</t>
+  </si>
+  <si>
+    <t>SeniorLAW Center</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 40000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Seniors Retirement, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c45c69cdc26493bab3ebddd2c4940fb-client-reception-and-intake-associate-seniorlaw-center-philadelphia</t>
+  </si>
+  <si>
+    <t>Communications &amp; Development Coordinator</t>
+  </si>
+  <si>
+    <t>Walpole, MA</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17360256948648bf9b8f8aeab4798b93-communications-development-coordinator-united-church-in-walpole-walpole</t>
+  </si>
+  <si>
+    <t>Communications &amp; Digital Engagement Associate/Manager</t>
+  </si>
+  <si>
+    <t>Environmental Advocates NY</t>
+  </si>
+  <si>
+    <t>Albany, NY</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/53db31c2f80e44c2b52cc17a4f4e0a36-communications-digital-engagement-associatemanager-environmental-advocates-ny-albany</t>
+  </si>
+  <si>
+    <t>Communications and Events Manager</t>
+  </si>
+  <si>
+    <t>West End House</t>
+  </si>
+  <si>
+    <t>USD 64500.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c6748da06534f4884d64e614d50523a-communications-and-events-manager-west-end-house-boston</t>
+  </si>
+  <si>
+    <t>Deputy Director - Portfolio Management</t>
+  </si>
+  <si>
+    <t>San Francisco Mayor’s Office of Housing and Community Development</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 170976.00 - 218218.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/7c607855ab8f4fa297e48380b09314c5-deputy-director-portfolio-management-san-francisco-mayors-office-of-housing-and-community-development-san-francisco</t>
+  </si>
+  <si>
+    <t>Deputy Director – Multifamily Housing and Homeownership</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/5b9e0129bd7b41419602a1beb60f698a-deputy-director-multifamily-housing-and-homeownership-san-francisco-mayors-office-of-housing-and-community-development-san-francisco</t>
+  </si>
+  <si>
+    <t>Development and Communications Coordinator</t>
+  </si>
+  <si>
+    <t>KIDS for the BAY</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 55000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8fd694a097344249a8a2f97d695a6cc1-development-and-communications-coordinator-kids-for-the-bay-berkeley</t>
+  </si>
+  <si>
+    <t>Development Manager, Grants &amp; Operations</t>
+  </si>
+  <si>
+    <t>Studio in a School Association</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 79000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79dcc3a91a2442c3a39de4a12d9146b7-development-manager-grants-operations-studio-in-a-school-association-new-york</t>
+  </si>
+  <si>
+    <t>Development Operations Associate</t>
+  </si>
+  <si>
+    <t>Reproductive Freedom for All</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c45e21500f4c453aa24750c11f892ff8-development-operations-associate-reproductive-freedom-for-all-washington</t>
+  </si>
+  <si>
+    <t>Development Special Events Associate</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/086d5b7d077749a58bb5a174556b1028-development-special-events-associate-reproductive-freedom-for-all-san-francisco</t>
+  </si>
+  <si>
+    <t>Digital Director, Central Communications</t>
+  </si>
+  <si>
+    <t>New America</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e769b40fe424505adec65202830ef2c-digital-director-central-communications-new-america-washington</t>
+  </si>
+  <si>
+    <t>Digital Marketing Coordinator</t>
+  </si>
+  <si>
+    <t>New England Botanic Garden at Tower Hill</t>
+  </si>
+  <si>
+    <t>Boylston, MA</t>
+  </si>
+  <si>
+    <t>USD 21.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75e3d7544acb4b42903e6ad7cfa4487a-digital-marketing-coordinator-new-england-botanic-garden-at-tower-hill-boylston</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Prep for Prep</t>
+  </si>
+  <si>
+    <t>USD 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2d9e31bd6d69476189e61c555697ed01-director-of-development-prep-for-prep-new-york</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14e15dd09a6245bdbbb4ab7d7096a1db-director-of-development-educated-choices-program-peachtree-corners</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Camelback Ventures</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ae0807af549944d09333ee5ccc345e6f-director-of-finance-camelback-ventures-new-orleans</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>School of VISUAL ARTS</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d0cbc26156ca477097f5ecdaf801a694-director-of-operations-school-of-visual-arts-new-york</t>
+  </si>
+  <si>
+    <t>Director, Public Programs</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db9c20f2508645ec849bcf6e1c533422-director-public-programs-studio-in-a-school-association-new-york</t>
+  </si>
+  <si>
+    <t>Donor Organizing - Program Associate</t>
+  </si>
+  <si>
+    <t>North Star Fund</t>
+  </si>
+  <si>
+    <t>USD 73337.00 - 73337.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f03253e6616434c922e9344b06676c8-donor-organizing-program-associate-north-star-fund-new-york</t>
+  </si>
+  <si>
+    <t>Early Childhood Education Program Facilitator</t>
+  </si>
+  <si>
+    <t>Smart from the Start, Inc.</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/75619facb9f746fb8a8487c452088e36-early-childhood-education-program-facilitator-smart-from-the-start-inc-washington</t>
+  </si>
+  <si>
+    <t>Education Manager, Academy of Rescue &amp; Conservation</t>
+  </si>
+  <si>
+    <t>International Fund for Animal Welfare - IFAW</t>
+  </si>
+  <si>
+    <t>Animals, Disaster Relief, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c19937d641cc4a77b34debed04caf08b-education-manager-academy-of-rescue-conservation-international-fund-for-animal-welfare-ifaw-washington</t>
+  </si>
+  <si>
+    <t>Ejecutivo Telefónico</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles y Juveniles SOS de México, I. A. P</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>MXN 9000.00 - 10000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bb53c7068c64b7dbeea64c1c4ece3d2-ejecutivo-telefonico-aldeas-infantiles-y-juveniles-sos-de-mexico-i-a-p-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Enterprise Sales Representative</t>
+  </si>
+  <si>
+    <t>Rescuing Leftover Cuisine</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1faa98bf4cd348a69b08e4f806bff280-enterprise-sales-representative-rescuing-leftover-cuisine-new-york</t>
+  </si>
+  <si>
+    <t>Executive Assistant - *Remote*</t>
+  </si>
+  <si>
+    <t>Compassion and Choices</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6e117ed9516f4daca436c8d16976d6eb-executive-assistant-remote-compassion-and-choices-washington</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>ArtsConnection</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbc42e35bac64589a6a81841dc847a1e-executive-director-artsconnection-new-york</t>
+  </si>
+  <si>
+    <t>Executive Facilitator + Nonprofit Collaboration Expert</t>
+  </si>
+  <si>
+    <t>New Sector Alliance</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d9696b38ebb454d9a6fb933454c12f4-executive-facilitator-nonprofit-collaboration-expert-new-sector-alliance-providence</t>
+  </si>
+  <si>
+    <t>Exhibition Technician (Part-Time)</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/946c97de3eeb451281b7b1df59857cdd-exhibition-technician-part-time-school-of-visual-arts-new-york</t>
+  </si>
+  <si>
+    <t>Facilities &amp; Administrative Coordinator</t>
+  </si>
+  <si>
+    <t>The James Irvine Foundation</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Job Workplace, Urban Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb27771740f74d2da68cace726d96e85-facilities-administrative-coordinator-the-james-irvine-foundation-san-francisco</t>
+  </si>
+  <si>
+    <t>Full-Time Compost Operator</t>
+  </si>
+  <si>
+    <t>Earth Matter NY Inc.</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b34cd1a4fce4df2966ede3f1cbdf85c-full-time-compost-operator-earth-matter-ny-inc-new-york</t>
+  </si>
+  <si>
+    <t>Grant Officer</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 84280.00 - 87685.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e48ad3e1d9043a8bcc7631a6fc908df-grant-officer-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Grants Database Manager</t>
+  </si>
+  <si>
+    <t>DC Bar Foundation</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a35fa81252c443609bbfbc8a4412ef6e-grants-database-manager-dc-bar-foundation-washington</t>
+  </si>
+  <si>
+    <t>Grants Financial Manager</t>
+  </si>
+  <si>
+    <t>Legal Aid Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5a5fdb91b9064fc3851881c382c6e77b-grants-financial-manager-legal-aid-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Immigration Attorney</t>
+  </si>
+  <si>
+    <t>NMIC (Northern Manhattan Improvement Corporation)</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 96000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08ac2deddae0480dbe88fadd06982ccb-immigration-attorney-nmic-northern-manhattan-improvement-corporation-new-york</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer, East Region</t>
+  </si>
+  <si>
+    <t>Facing History and Ourselves</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6298543fe00844eb91e30cc8e5dde03f-major-gifts-officer-east-region-facing-history-and-ourselves-boston</t>
+  </si>
+  <si>
+    <t>Managing Appeals Attorney, Detained Adult Program</t>
+  </si>
+  <si>
+    <t>Amica Center for Immigrant Rights (Amica Center)</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3136615153394196afd698a80824e608-managing-appeals-attorney-detained-adult-program-amica-center-for-immigrant-rights-amica-center-washington</t>
+  </si>
+  <si>
+    <t>Part Time Arts Administrator - Education Program Assistant</t>
+  </si>
+  <si>
+    <t>Day Eight</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/15f6bb03b5054faab310d986d987993b-part-time-arts-administrator-education-program-assistant-day-eight-washington</t>
+  </si>
+  <si>
+    <t>Part Time Marketing Associate</t>
+  </si>
+  <si>
+    <t>Person-to-Person, Inc.</t>
+  </si>
+  <si>
+    <t>Darien, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f8c4398070b6403e92584fab52a56337-part-time-marketing-associate-person-to-person-inc-darien</t>
+  </si>
+  <si>
+    <t>Part-time Community Organizer</t>
+  </si>
+  <si>
+    <t>Arab American Association of New York</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/453ee67ee2654bebb1bb915d0b0f803f-part-time-community-organizer-arab-american-association-of-new-york-kings-county</t>
+  </si>
+  <si>
+    <t>Peer Review Support Assistant</t>
+  </si>
+  <si>
+    <t>American Meteorological Society</t>
+  </si>
+  <si>
+    <t>USD 48500.00 - 50500.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9aa5bb796694c2e9ea7c32e72525495-peer-review-support-assistant-american-meteorological-society-boston</t>
+  </si>
+  <si>
+    <t>Policy Director</t>
+  </si>
+  <si>
+    <t>Environmental and Energy Study Institute</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/11a64b0d6d4a4c69a726e27bd34f1261-policy-director-environmental-and-energy-study-institute-washington</t>
+  </si>
+  <si>
+    <t>Professional Advancement Program Manager</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9845aa5e32b841109878186342feeada-professional-advancement-program-manager-prep-for-prep-new-york</t>
+  </si>
+  <si>
+    <t>Program Associate</t>
+  </si>
+  <si>
+    <t>Amazon Conservation Association</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f694e7050c7f4991b0f599b0d855c081-program-associate-amazon-conservation-association-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/911d6b5974e14140a022064fb894db78-program-coordinator-smart-from-the-start-inc-washington</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>college point, New York</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a500e162867e49c69263a2ed885df7f1-program-director-careers-in-nonprofits-inc-college-point</t>
+  </si>
+  <si>
+    <t>Public Safety Manager</t>
+  </si>
+  <si>
+    <t>Downtown Brooklyn Partnership</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Urban Areas, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7bf97450c8f45138d5d07685b01acfe-public-safety-manager-downtown-brooklyn-partnership-kings-county</t>
+  </si>
+  <si>
+    <t>Responsable de Articulación Operacional y Médica</t>
+  </si>
+  <si>
+    <t>MÉDICOS SIN FRONTERAS LAT</t>
+  </si>
+  <si>
+    <t>Bogotá, Bogotá, CO</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/865a6c51fa1448f09c8ea078b7241f80-responsable-de-articulacion-operacional-y-medica-medicos-sin-fronteras-lat-bogota</t>
+  </si>
+  <si>
+    <t>Samaritans Training Coordinator</t>
+  </si>
+  <si>
+    <t>Family Services of the Merrimack Valley, Inc</t>
+  </si>
+  <si>
+    <t>Lawrence, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 22.00/hour</t>
+  </si>
+  <si>
+    <t>Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6136a6fd6a504fc6992e8f9512e4b69d-samaritans-training-coordinator-family-services-of-the-merrimack-valley-inc-lawrence</t>
+  </si>
+  <si>
+    <t>SANCTUARY ADMINISTRATOR - AMAZON JUNGLE</t>
+  </si>
+  <si>
+    <t>santa cruz, Santa Cruz, BO</t>
+  </si>
+  <si>
+    <t>BOB 2000.00 - 3000.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Community Development, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9cfb8f5a3ac54c7aba4d10dd75f9302a-sanctuary-administrator-amazon-jungle-comunidad-inti-wara-yassi-ciwy-santa-cruz</t>
+  </si>
+  <si>
+    <t>School Year Math Teacher</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 48.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b937e0f76724583953315d174c3e1ab-school-year-math-teacher-prep-for-prep-new-york</t>
+  </si>
+  <si>
+    <t>Senior Associate</t>
+  </si>
+  <si>
+    <t>Nonprofit Professionals Advisory Group</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/a175520e662e4042a58410f9248bafb9-senior-associate-nonprofit-professionals-advisory-group-beaverton</t>
+  </si>
+  <si>
+    <t>Senior Director, Global Accounting</t>
+  </si>
+  <si>
+    <t>Cure Blindness Project</t>
+  </si>
+  <si>
+    <t>USD 116400.00 - 149100.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82816d7eaeea48edb5fe9329cee75a88-senior-director-global-accounting-cure-blindness-project-norwich</t>
+  </si>
+  <si>
+    <t>Senior Finance and Accounting Manager</t>
+  </si>
+  <si>
+    <t>Baltic Street Wellness Solutions</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Human Rights Civil Liberties, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a479767d81134262921b4acd9ddf6c5f-senior-finance-and-accounting-manager-baltic-street-wellness-solutions-kings-county</t>
+  </si>
+  <si>
+    <t>Senior Manager of Institutional Relations</t>
+  </si>
+  <si>
+    <t>Bridge Over Troubled Waters</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ed8babf2555b4c5381dc67164b5f4800-senior-manager-of-institutional-relations-bridge-over-troubled-waters-boston</t>
+  </si>
+  <si>
+    <t>Senior Manager, Partner Relations</t>
+  </si>
+  <si>
+    <t>Benetech</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a2ac55743506481989906c300a08efb6-senior-manager-partner-relations-benetech-palo-alto</t>
+  </si>
+  <si>
+    <t>Senior Manager, Payroll Operations &amp; Accounting</t>
+  </si>
+  <si>
+    <t>Partners for Rural Impact</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b76f2553ac548b5b9f01dfb33db426a-senior-manager-payroll-operations-accounting-partners-for-rural-impact-berea</t>
+  </si>
+  <si>
+    <t>Senior Project Manager of Shelter Systems and Rapid Resolution</t>
+  </si>
+  <si>
+    <t>Partners for HOME</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 86000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/603c557337ee4bee9424aaf7b471a199-senior-project-manager-of-shelter-systems-and-rapid-resolution-partners-for-home-atlanta</t>
+  </si>
+  <si>
+    <t>Service Coordinator</t>
+  </si>
+  <si>
+    <t>Green City Force</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Energy, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ad31043be0240e8b6c7c5a1a830be62-service-coordinator-green-city-force-kings-county</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/292412b4012f4c108c64488d4d4a61eb-service-enriched-housing-super-hero-community-housing-resource-partners-inc-houston</t>
+  </si>
+  <si>
+    <t>Speech Therapist</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68986ca7e89f4ea48f6dfb568517024f-speech-therapist-youth-villages-memphis</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>American Association for Justice</t>
+  </si>
+  <si>
+    <t>USD 68600.00 - 81900.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c8491f1797d2471c8b439ca4afd7344d-staff-accountant-american-association-for-justice-washington</t>
+  </si>
+  <si>
+    <t>Suicide Prevention Services Manager</t>
+  </si>
+  <si>
+    <t>FAMILY SERVICE AGENCY OF THE CENTRAL COAST</t>
+  </si>
+  <si>
+    <t>Salinas, California</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 38.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/58991cfc93ab4ea5a1d6b96de7c4c9bb-suicide-prevention-services-manager-family-service-agency-of-the-central-coast-salinas</t>
+  </si>
+  <si>
+    <t>Supervising Housing Attorney</t>
+  </si>
+  <si>
+    <t>USD 104880.00 - 118128.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Housing Homelessness, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af5fab135c0b4db3b315b90a4a51a8d2-supervising-housing-attorney-nmic-northern-manhattan-improvement-corporation-new-york</t>
+  </si>
+  <si>
+    <t>Veterinario Principal - trabajar con la fauna silvestre en la selva boliviana</t>
+  </si>
+  <si>
+    <t>San Buenaventur, san buenaventura, BO</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f11d5d3271094b7495061ad396c05023-veterinario-principal-trabajar-con-la-fauna-silvestre-en-la-selva-boliviana-comunidad-inti-wara-yassi-ciwy-san-buenaventur</t>
+  </si>
+  <si>
+    <t>Vice President of People &amp; Culture</t>
+  </si>
+  <si>
+    <t>Future Now</t>
+  </si>
+  <si>
+    <t>USD 217518.00 - 228394.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/2e383ed1b9634c5aa1353fc96bf6562b-vice-president-of-people-culture-future-now-hartford</t>
+  </si>
+  <si>
+    <t>Workforce Cafe Coordinator, Workforce Development</t>
+  </si>
+  <si>
+    <t>Bread for the City</t>
+  </si>
+  <si>
+    <t>USD 25.04 - 26.44/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95bdc19936474960bbe73860ab09584c-workforce-cafe-coordinator-workforce-development-bread-for-the-city-washington</t>
+  </si>
+  <si>
+    <t>Youth Program Therapist and Manager</t>
+  </si>
+  <si>
+    <t>The Healing Center Seattle</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>Mental Health, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8f68c35c089455182cdfa0832688c0b-youth-program-therapist-and-manager-the-healing-center-seattle-seattle</t>
+  </si>
+  <si>
+    <t>DIRECTOR OF RESEARCH</t>
+  </si>
+  <si>
+    <t>Central Texas Food Bank</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>https://members.foodsystemsnetwork.org/classifieds/moreinfo.php?cid=72386071</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1710,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1736,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2079,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2118,634 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" t="s">
+        <v>111</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" t="s">
+        <v>123</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" t="s">
+        <v>129</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>143</v>
+      </c>
+      <c r="F26" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>152</v>
+      </c>
+      <c r="F27" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +2801,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +2840,1978 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E3" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F4" t="s">
+        <v>173</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F6" t="s">
+        <v>186</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E8" t="s">
+        <v>196</v>
+      </c>
+      <c r="F8" t="s">
+        <v>197</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" t="s">
+        <v>201</v>
+      </c>
+      <c r="D9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F10" t="s">
+        <v>209</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D11" t="s">
+        <v>171</v>
+      </c>
+      <c r="E11" t="s">
+        <v>214</v>
+      </c>
+      <c r="F11" t="s">
+        <v>215</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>217</v>
+      </c>
+      <c r="B12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C12" t="s">
+        <v>219</v>
+      </c>
+      <c r="D12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>223</v>
+      </c>
+      <c r="B13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" t="s">
+        <v>224</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E14" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" t="s">
+        <v>230</v>
+      </c>
+      <c r="C15" t="s">
+        <v>231</v>
+      </c>
+      <c r="D15" t="s">
+        <v>158</v>
+      </c>
+      <c r="E15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F15" t="s">
+        <v>233</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" t="s">
+        <v>238</v>
+      </c>
+      <c r="F16" t="s">
+        <v>238</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" t="s">
+        <v>241</v>
+      </c>
+      <c r="C17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" t="s">
+        <v>243</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>245</v>
+      </c>
+      <c r="B18" t="s">
+        <v>246</v>
+      </c>
+      <c r="C18" t="s">
+        <v>247</v>
+      </c>
+      <c r="D18" t="s">
+        <v>165</v>
+      </c>
+      <c r="E18" t="s">
+        <v>248</v>
+      </c>
+      <c r="F18" t="s">
+        <v>167</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>250</v>
+      </c>
+      <c r="B19" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E19" t="s">
+        <v>253</v>
+      </c>
+      <c r="F19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>256</v>
+      </c>
+      <c r="B20" t="s">
+        <v>246</v>
+      </c>
+      <c r="C20" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20" t="s">
+        <v>258</v>
+      </c>
+      <c r="F20" t="s">
+        <v>167</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>260</v>
+      </c>
+      <c r="B21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C21" t="s">
+        <v>262</v>
+      </c>
+      <c r="D21" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" t="s">
+        <v>263</v>
+      </c>
+      <c r="F21" t="s">
+        <v>264</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>266</v>
+      </c>
+      <c r="B22" t="s">
+        <v>267</v>
+      </c>
+      <c r="C22" t="s">
+        <v>201</v>
+      </c>
+      <c r="D22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" t="s">
+        <v>268</v>
+      </c>
+      <c r="F22" t="s">
+        <v>269</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" t="s">
+        <v>274</v>
+      </c>
+      <c r="F23" t="s">
+        <v>275</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>277</v>
+      </c>
+      <c r="B24" t="s">
+        <v>272</v>
+      </c>
+      <c r="C24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D24" t="s">
+        <v>158</v>
+      </c>
+      <c r="E24" t="s">
+        <v>274</v>
+      </c>
+      <c r="F24" t="s">
+        <v>275</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>279</v>
+      </c>
+      <c r="B25" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" t="s">
+        <v>281</v>
+      </c>
+      <c r="D25" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" t="s">
+        <v>282</v>
+      </c>
+      <c r="F25" t="s">
+        <v>283</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" t="s">
+        <v>286</v>
+      </c>
+      <c r="C26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" t="s">
+        <v>158</v>
+      </c>
+      <c r="E26" t="s">
+        <v>287</v>
+      </c>
+      <c r="F26" t="s">
+        <v>269</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>289</v>
+      </c>
+      <c r="B27" t="s">
+        <v>290</v>
+      </c>
+      <c r="C27" t="s">
+        <v>291</v>
+      </c>
+      <c r="D27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" t="s">
+        <v>292</v>
+      </c>
+      <c r="F27" t="s">
+        <v>293</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>295</v>
+      </c>
+      <c r="B28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28" t="s">
+        <v>273</v>
+      </c>
+      <c r="D28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E28" t="s">
+        <v>292</v>
+      </c>
+      <c r="F28" t="s">
+        <v>293</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" t="s">
+        <v>298</v>
+      </c>
+      <c r="C29" t="s">
+        <v>291</v>
+      </c>
+      <c r="D29" t="s">
+        <v>158</v>
+      </c>
+      <c r="E29" t="s">
+        <v>299</v>
+      </c>
+      <c r="F29" t="s">
+        <v>300</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>302</v>
+      </c>
+      <c r="B30" t="s">
+        <v>303</v>
+      </c>
+      <c r="C30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D30" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" t="s">
+        <v>305</v>
+      </c>
+      <c r="F30" t="s">
+        <v>306</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>308</v>
+      </c>
+      <c r="B31" t="s">
+        <v>309</v>
+      </c>
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+      <c r="D31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" t="s">
+        <v>310</v>
+      </c>
+      <c r="F31" t="s">
+        <v>238</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>308</v>
+      </c>
+      <c r="B32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" t="s">
+        <v>190</v>
+      </c>
+      <c r="D32" t="s">
+        <v>158</v>
+      </c>
+      <c r="E32" t="s">
+        <v>312</v>
+      </c>
+      <c r="F32" t="s">
+        <v>313</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>315</v>
+      </c>
+      <c r="B33" t="s">
+        <v>316</v>
+      </c>
+      <c r="C33" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" t="s">
+        <v>158</v>
+      </c>
+      <c r="E33" t="s">
+        <v>317</v>
+      </c>
+      <c r="F33" t="s">
+        <v>318</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>320</v>
+      </c>
+      <c r="B34" t="s">
+        <v>321</v>
+      </c>
+      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" t="s">
+        <v>158</v>
+      </c>
+      <c r="E34" t="s">
+        <v>322</v>
+      </c>
+      <c r="F34" t="s">
+        <v>203</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>324</v>
+      </c>
+      <c r="B35" t="s">
+        <v>286</v>
+      </c>
+      <c r="C35" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" t="s">
+        <v>325</v>
+      </c>
+      <c r="F35" t="s">
+        <v>269</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>327</v>
+      </c>
+      <c r="B36" t="s">
+        <v>328</v>
+      </c>
+      <c r="C36" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" t="s">
+        <v>329</v>
+      </c>
+      <c r="F36" t="s">
+        <v>330</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>332</v>
+      </c>
+      <c r="B37" t="s">
+        <v>333</v>
+      </c>
+      <c r="C37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D37" t="s">
+        <v>165</v>
+      </c>
+      <c r="E37" t="s">
+        <v>334</v>
+      </c>
+      <c r="F37" t="s">
+        <v>335</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>337</v>
+      </c>
+      <c r="B38" t="s">
+        <v>338</v>
+      </c>
+      <c r="C38" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" t="s">
+        <v>178</v>
+      </c>
+      <c r="E38" t="s">
+        <v>263</v>
+      </c>
+      <c r="F38" t="s">
+        <v>339</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>341</v>
+      </c>
+      <c r="B39" t="s">
+        <v>342</v>
+      </c>
+      <c r="C39" t="s">
+        <v>343</v>
+      </c>
+      <c r="D39" t="s">
+        <v>158</v>
+      </c>
+      <c r="E39" t="s">
+        <v>344</v>
+      </c>
+      <c r="F39" t="s">
+        <v>345</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>347</v>
+      </c>
+      <c r="B40" t="s">
+        <v>348</v>
+      </c>
+      <c r="C40" t="s">
+        <v>349</v>
+      </c>
+      <c r="D40" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" t="s">
+        <v>350</v>
+      </c>
+      <c r="F40" t="s">
+        <v>351</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>353</v>
+      </c>
+      <c r="B41" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" t="s">
+        <v>190</v>
+      </c>
+      <c r="D41" t="s">
+        <v>158</v>
+      </c>
+      <c r="E41" t="s">
+        <v>202</v>
+      </c>
+      <c r="F41" t="s">
+        <v>355</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>357</v>
+      </c>
+      <c r="B42" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42" t="s">
+        <v>170</v>
+      </c>
+      <c r="D42" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" t="s">
+        <v>359</v>
+      </c>
+      <c r="F42" t="s">
+        <v>269</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>361</v>
+      </c>
+      <c r="B43" t="s">
+        <v>362</v>
+      </c>
+      <c r="C43" t="s">
+        <v>363</v>
+      </c>
+      <c r="D43" t="s">
+        <v>364</v>
+      </c>
+      <c r="E43" t="s">
+        <v>238</v>
+      </c>
+      <c r="F43" t="s">
+        <v>365</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>367</v>
+      </c>
+      <c r="B44" t="s">
+        <v>321</v>
+      </c>
+      <c r="C44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" t="s">
+        <v>165</v>
+      </c>
+      <c r="E44" t="s">
+        <v>368</v>
+      </c>
+      <c r="F44" t="s">
+        <v>203</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>370</v>
+      </c>
+      <c r="B45" t="s">
+        <v>371</v>
+      </c>
+      <c r="C45" t="s">
+        <v>372</v>
+      </c>
+      <c r="D45" t="s">
+        <v>158</v>
+      </c>
+      <c r="E45" t="s">
+        <v>373</v>
+      </c>
+      <c r="F45" t="s">
+        <v>374</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>376</v>
+      </c>
+      <c r="B46" t="s">
+        <v>377</v>
+      </c>
+      <c r="C46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" t="s">
+        <v>258</v>
+      </c>
+      <c r="F46" t="s">
+        <v>378</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>380</v>
+      </c>
+      <c r="B47" t="s">
+        <v>381</v>
+      </c>
+      <c r="C47" t="s">
+        <v>170</v>
+      </c>
+      <c r="D47" t="s">
+        <v>158</v>
+      </c>
+      <c r="E47" t="s">
+        <v>382</v>
+      </c>
+      <c r="F47" t="s">
+        <v>383</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>385</v>
+      </c>
+      <c r="B48" t="s">
+        <v>386</v>
+      </c>
+      <c r="C48" t="s">
+        <v>387</v>
+      </c>
+      <c r="D48" t="s">
+        <v>158</v>
+      </c>
+      <c r="E48" t="s">
+        <v>388</v>
+      </c>
+      <c r="F48" t="s">
+        <v>238</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>390</v>
+      </c>
+      <c r="B49" t="s">
+        <v>391</v>
+      </c>
+      <c r="C49" t="s">
+        <v>392</v>
+      </c>
+      <c r="D49" t="s">
+        <v>158</v>
+      </c>
+      <c r="E49" t="s">
+        <v>393</v>
+      </c>
+      <c r="F49" t="s">
+        <v>383</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>395</v>
+      </c>
+      <c r="B50" t="s">
+        <v>396</v>
+      </c>
+      <c r="C50" t="s">
+        <v>170</v>
+      </c>
+      <c r="D50" t="s">
+        <v>158</v>
+      </c>
+      <c r="E50" t="s">
+        <v>397</v>
+      </c>
+      <c r="F50" t="s">
+        <v>398</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>400</v>
+      </c>
+      <c r="B51" t="s">
+        <v>401</v>
+      </c>
+      <c r="C51" t="s">
+        <v>201</v>
+      </c>
+      <c r="D51" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" t="s">
+        <v>402</v>
+      </c>
+      <c r="F51" t="s">
+        <v>403</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>405</v>
+      </c>
+      <c r="B52" t="s">
+        <v>406</v>
+      </c>
+      <c r="C52" t="s">
+        <v>291</v>
+      </c>
+      <c r="D52" t="s">
+        <v>158</v>
+      </c>
+      <c r="E52" t="s">
+        <v>407</v>
+      </c>
+      <c r="F52" t="s">
+        <v>238</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>409</v>
+      </c>
+      <c r="B53" t="s">
+        <v>410</v>
+      </c>
+      <c r="C53" t="s">
+        <v>291</v>
+      </c>
+      <c r="D53" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53" t="s">
+        <v>411</v>
+      </c>
+      <c r="F53" t="s">
+        <v>412</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>414</v>
+      </c>
+      <c r="B54" t="s">
+        <v>415</v>
+      </c>
+      <c r="C54" t="s">
+        <v>416</v>
+      </c>
+      <c r="D54" t="s">
+        <v>165</v>
+      </c>
+      <c r="E54" t="s">
+        <v>417</v>
+      </c>
+      <c r="F54" t="s">
+        <v>418</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>420</v>
+      </c>
+      <c r="B55" t="s">
+        <v>421</v>
+      </c>
+      <c r="C55" t="s">
+        <v>422</v>
+      </c>
+      <c r="D55" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" t="s">
+        <v>423</v>
+      </c>
+      <c r="F55" t="s">
+        <v>238</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>425</v>
+      </c>
+      <c r="B56" t="s">
+        <v>426</v>
+      </c>
+      <c r="C56" t="s">
+        <v>201</v>
+      </c>
+      <c r="D56" t="s">
+        <v>158</v>
+      </c>
+      <c r="E56" t="s">
+        <v>427</v>
+      </c>
+      <c r="F56" t="s">
+        <v>428</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>430</v>
+      </c>
+      <c r="B57" t="s">
+        <v>431</v>
+      </c>
+      <c r="C57" t="s">
+        <v>291</v>
+      </c>
+      <c r="D57" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s">
+        <v>432</v>
+      </c>
+      <c r="F57" t="s">
+        <v>433</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>435</v>
+      </c>
+      <c r="B58" t="s">
+        <v>309</v>
+      </c>
+      <c r="C58" t="s">
+        <v>170</v>
+      </c>
+      <c r="D58" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" t="s">
+        <v>436</v>
+      </c>
+      <c r="F58" t="s">
+        <v>238</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>438</v>
+      </c>
+      <c r="B59" t="s">
+        <v>439</v>
+      </c>
+      <c r="C59" t="s">
+        <v>291</v>
+      </c>
+      <c r="D59" t="s">
+        <v>158</v>
+      </c>
+      <c r="E59" t="s">
+        <v>440</v>
+      </c>
+      <c r="F59" t="s">
+        <v>441</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>443</v>
+      </c>
+      <c r="B60" t="s">
+        <v>333</v>
+      </c>
+      <c r="C60" t="s">
+        <v>291</v>
+      </c>
+      <c r="D60" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" t="s">
+        <v>232</v>
+      </c>
+      <c r="F60" t="s">
+        <v>335</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>445</v>
+      </c>
+      <c r="B61" t="s">
+        <v>446</v>
+      </c>
+      <c r="C61" t="s">
+        <v>447</v>
+      </c>
+      <c r="D61" t="s">
+        <v>158</v>
+      </c>
+      <c r="E61" t="s">
+        <v>448</v>
+      </c>
+      <c r="F61" t="s">
+        <v>238</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>450</v>
+      </c>
+      <c r="B62" t="s">
+        <v>451</v>
+      </c>
+      <c r="C62" t="s">
+        <v>422</v>
+      </c>
+      <c r="D62" t="s">
+        <v>158</v>
+      </c>
+      <c r="E62" t="s">
+        <v>452</v>
+      </c>
+      <c r="F62" t="s">
+        <v>453</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>455</v>
+      </c>
+      <c r="B63" t="s">
+        <v>456</v>
+      </c>
+      <c r="C63" t="s">
+        <v>457</v>
+      </c>
+      <c r="D63" t="s">
+        <v>158</v>
+      </c>
+      <c r="E63" t="s">
+        <v>238</v>
+      </c>
+      <c r="F63" t="s">
+        <v>458</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>460</v>
+      </c>
+      <c r="B64" t="s">
+        <v>461</v>
+      </c>
+      <c r="C64" t="s">
+        <v>462</v>
+      </c>
+      <c r="D64" t="s">
+        <v>158</v>
+      </c>
+      <c r="E64" t="s">
+        <v>463</v>
+      </c>
+      <c r="F64" t="s">
+        <v>464</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>466</v>
+      </c>
+      <c r="B65" t="s">
+        <v>176</v>
+      </c>
+      <c r="C65" t="s">
+        <v>467</v>
+      </c>
+      <c r="D65" t="s">
+        <v>158</v>
+      </c>
+      <c r="E65" t="s">
+        <v>468</v>
+      </c>
+      <c r="F65" t="s">
+        <v>469</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>471</v>
+      </c>
+      <c r="B66" t="s">
+        <v>309</v>
+      </c>
+      <c r="C66" t="s">
+        <v>170</v>
+      </c>
+      <c r="D66" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" t="s">
+        <v>472</v>
+      </c>
+      <c r="F66" t="s">
+        <v>238</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>474</v>
+      </c>
+      <c r="B67" t="s">
+        <v>475</v>
+      </c>
+      <c r="C67" t="s">
+        <v>190</v>
+      </c>
+      <c r="D67" t="s">
+        <v>158</v>
+      </c>
+      <c r="E67" t="s">
+        <v>476</v>
+      </c>
+      <c r="F67" t="s">
+        <v>477</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>479</v>
+      </c>
+      <c r="B68" t="s">
+        <v>480</v>
+      </c>
+      <c r="C68" t="s">
+        <v>190</v>
+      </c>
+      <c r="D68" t="s">
+        <v>158</v>
+      </c>
+      <c r="E68" t="s">
+        <v>481</v>
+      </c>
+      <c r="F68" t="s">
+        <v>482</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>484</v>
+      </c>
+      <c r="B69" t="s">
+        <v>485</v>
+      </c>
+      <c r="C69" t="s">
+        <v>422</v>
+      </c>
+      <c r="D69" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" t="s">
+        <v>486</v>
+      </c>
+      <c r="F69" t="s">
+        <v>487</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>489</v>
+      </c>
+      <c r="B70" t="s">
+        <v>490</v>
+      </c>
+      <c r="C70" t="s">
+        <v>201</v>
+      </c>
+      <c r="D70" t="s">
+        <v>158</v>
+      </c>
+      <c r="E70" t="s">
+        <v>407</v>
+      </c>
+      <c r="F70" t="s">
+        <v>491</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>493</v>
+      </c>
+      <c r="B71" t="s">
+        <v>494</v>
+      </c>
+      <c r="C71" t="s">
+        <v>190</v>
+      </c>
+      <c r="D71" t="s">
+        <v>158</v>
+      </c>
+      <c r="E71" t="s">
+        <v>495</v>
+      </c>
+      <c r="F71" t="s">
+        <v>496</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>498</v>
+      </c>
+      <c r="B72" t="s">
+        <v>499</v>
+      </c>
+      <c r="C72" t="s">
+        <v>190</v>
+      </c>
+      <c r="D72" t="s">
+        <v>158</v>
+      </c>
+      <c r="E72" t="s">
+        <v>238</v>
+      </c>
+      <c r="F72" t="s">
+        <v>500</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>502</v>
+      </c>
+      <c r="B73" t="s">
+        <v>503</v>
+      </c>
+      <c r="C73" t="s">
+        <v>504</v>
+      </c>
+      <c r="D73" t="s">
+        <v>158</v>
+      </c>
+      <c r="E73" t="s">
+        <v>505</v>
+      </c>
+      <c r="F73" t="s">
+        <v>275</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>507</v>
+      </c>
+      <c r="B74" t="s">
+        <v>508</v>
+      </c>
+      <c r="C74" t="s">
+        <v>422</v>
+      </c>
+      <c r="D74" t="s">
+        <v>158</v>
+      </c>
+      <c r="E74" t="s">
+        <v>509</v>
+      </c>
+      <c r="F74" t="s">
+        <v>510</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>512</v>
+      </c>
+      <c r="B75" t="s">
+        <v>513</v>
+      </c>
+      <c r="C75" t="s">
+        <v>514</v>
+      </c>
+      <c r="D75" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" t="s">
+        <v>515</v>
+      </c>
+      <c r="F75" t="s">
+        <v>516</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>518</v>
+      </c>
+      <c r="B76" t="s">
+        <v>519</v>
+      </c>
+      <c r="C76" t="s">
+        <v>520</v>
+      </c>
+      <c r="D76" t="s">
+        <v>158</v>
+      </c>
+      <c r="E76" t="s">
+        <v>238</v>
+      </c>
+      <c r="F76" t="s">
+        <v>521</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>523</v>
+      </c>
+      <c r="B77" t="s">
+        <v>524</v>
+      </c>
+      <c r="C77" t="s">
+        <v>291</v>
+      </c>
+      <c r="D77" t="s">
+        <v>158</v>
+      </c>
+      <c r="E77" t="s">
+        <v>525</v>
+      </c>
+      <c r="F77" t="s">
+        <v>526</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>528</v>
+      </c>
+      <c r="B78" t="s">
+        <v>529</v>
+      </c>
+      <c r="C78" t="s">
+        <v>530</v>
+      </c>
+      <c r="D78" t="s">
+        <v>158</v>
+      </c>
+      <c r="E78" t="s">
+        <v>531</v>
+      </c>
+      <c r="F78" t="s">
+        <v>464</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>533</v>
+      </c>
+      <c r="B79" t="s">
+        <v>396</v>
+      </c>
+      <c r="C79" t="s">
+        <v>170</v>
+      </c>
+      <c r="D79" t="s">
+        <v>158</v>
+      </c>
+      <c r="E79" t="s">
+        <v>534</v>
+      </c>
+      <c r="F79" t="s">
+        <v>535</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>537</v>
+      </c>
+      <c r="B80" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" t="s">
+        <v>538</v>
+      </c>
+      <c r="D80" t="s">
+        <v>158</v>
+      </c>
+      <c r="E80" t="s">
+        <v>468</v>
+      </c>
+      <c r="F80" t="s">
+        <v>539</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>541</v>
+      </c>
+      <c r="B81" t="s">
+        <v>542</v>
+      </c>
+      <c r="C81" t="s">
+        <v>190</v>
+      </c>
+      <c r="D81" t="s">
+        <v>158</v>
+      </c>
+      <c r="E81" t="s">
+        <v>543</v>
+      </c>
+      <c r="F81" t="s">
+        <v>238</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>545</v>
+      </c>
+      <c r="B82" t="s">
+        <v>546</v>
+      </c>
+      <c r="C82" t="s">
+        <v>291</v>
+      </c>
+      <c r="D82" t="s">
+        <v>171</v>
+      </c>
+      <c r="E82" t="s">
+        <v>547</v>
+      </c>
+      <c r="F82" t="s">
+        <v>548</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>550</v>
+      </c>
+      <c r="B83" t="s">
+        <v>551</v>
+      </c>
+      <c r="C83" t="s">
+        <v>552</v>
+      </c>
+      <c r="D83" t="s">
+        <v>165</v>
+      </c>
+      <c r="E83" t="s">
+        <v>214</v>
+      </c>
+      <c r="F83" t="s">
+        <v>553</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -562,7 +4819,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -601,8 +4858,34 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B2" t="s">
+        <v>556</v>
+      </c>
+      <c r="C2" t="s">
+        <v>557</v>
+      </c>
+      <c r="D2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" t="s">
+        <v>558</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-17.xlsx
+++ b/docs/xlsx/jobs-2026-09-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="810">
   <si>
     <t>Title</t>
   </si>
@@ -562,6 +562,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/d434ca7b8e914b13af3061c80a827352-admninistradora-santuario-amazonas-boliviano-comunidad-inti-wara-yassi-ciwy-santa-cruz</t>
   </si>
   <si>
+    <t>Advancement Director, Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03cc824276ac400cb33fa767e293f0f1-advancement-director-mid-atlantic-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Affirmative Unit, Staff Attorney</t>
+  </si>
+  <si>
+    <t>Canal Alliance - Marin, California</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1702d888a90e43b7896b264b242de080-affirmative-unit-staff-attorney-canal-alliance-marin-california-san-rafael</t>
+  </si>
+  <si>
+    <t>After-Hours Counselor</t>
+  </si>
+  <si>
+    <t>Hope House in Crotona Park</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Housing Homelessness, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c61d3998f194e61b08272d236e0a71f-after-hours-counselor-hope-house-in-crotona-park-bronx-county</t>
+  </si>
+  <si>
     <t>Aftercare Associate</t>
   </si>
   <si>
@@ -580,15 +634,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/5b85e597bd5c494fba4cdab020f4d444-aftercare-associate-ace-association-of-community-employment-programs-for-the-homeless-inc-queens-county</t>
   </si>
   <si>
+    <t>AgriSea Sales and Operations Associate</t>
+  </si>
+  <si>
+    <t>GreenWave</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Agriculture, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bed6658ec0e64c0e8f109e3115722cc7-agrisea-sales-and-operations-associate-greenwave-new-haven</t>
+  </si>
+  <si>
     <t>Annual Giving &amp; Grants Manager</t>
   </si>
   <si>
     <t>Educated Choices Program</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 65000.00 - 75000.00/year</t>
   </si>
   <si>
@@ -598,6 +667,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/21dbc1f8fe014449abb6e542151862ec-annual-giving-grants-manager-educated-choices-program-lawrenceville</t>
   </si>
   <si>
+    <t>Assistant Director of Clinical Services</t>
+  </si>
+  <si>
+    <t>Seneca Family of Agencies</t>
+  </si>
+  <si>
+    <t>Monterey, California</t>
+  </si>
+  <si>
+    <t>USD 103434.00 - 117434.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dcb100bcb3114687b52cc9d0cd313e81-assistant-director-of-clinical-services-seneca-family-of-agencies-monterey</t>
+  </si>
+  <si>
     <t>Assistant Director, Grants and Administration</t>
   </si>
   <si>
@@ -685,6 +772,117 @@
     <t>https://www.idealist.org/en/nonprofit-job/8e9cbd0afd3b44a6986dae2a3edc5caa-beyond-te-youth-program-manager-center-for-teen-empowerment-somerville</t>
   </si>
   <si>
+    <t>Bilingual Digital Organizer</t>
+  </si>
+  <si>
+    <t>Patients For Affordable Drugs</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9006335fcaf74e31970aedc7cd0b1fa1-bilingual-digital-organizer-patients-for-affordable-drugs-washington</t>
+  </si>
+  <si>
+    <t>Bilingual Outreach Manager</t>
+  </si>
+  <si>
+    <t>The Senior Source, Senior Citizens of Greater Dallas</t>
+  </si>
+  <si>
+    <t>Dallas, Texas</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/864e11daecbe4811b7586155faf88de7-bilingual-outreach-manager-the-senior-source-senior-citizens-of-greater-dallas-dallas</t>
+  </si>
+  <si>
+    <t>Bilingual Social Worker</t>
+  </si>
+  <si>
+    <t>Central Union Mission</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8047b797bb634da783dd1a618758caa7-bilingual-social-worker-central-union-mission-arlington</t>
+  </si>
+  <si>
+    <t>Bilingual Staff Attorney (English-Spanish)</t>
+  </si>
+  <si>
+    <t>Life Span</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Legal Assistance, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7f5c6542d17b4893a8aa5e20ac13e313-bilingual-staff-attorney-english-spanish-life-span-chicago</t>
+  </si>
+  <si>
+    <t>Building Maintenance Technician</t>
+  </si>
+  <si>
+    <t>USD 42500.00 - 42500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2886112b2fd643fc8eee0b509340e176-building-maintenance-technician-hope-house-in-crotona-park-bronx-county</t>
+  </si>
+  <si>
+    <t>Canvass Team Lead and Volunteer Coordinator - STV</t>
+  </si>
+  <si>
+    <t>Center for Empowered Politics</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>USD 1440.00 - 1440.00/week</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/2b31853648fb4615aa81f794064a673e-canvass-team-lead-and-volunteer-coordinator-stv-center-for-empowered-politics-san-antonio</t>
+  </si>
+  <si>
+    <t>Canvasser</t>
+  </si>
+  <si>
+    <t>Make the Road Action</t>
+  </si>
+  <si>
+    <t>Perth Amboy, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 21.59 - 21.59/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67338e2ff8884c14a7c6aa8062f76ac8-canvasser-make-the-road-action-perth-amboy</t>
+  </si>
+  <si>
     <t>Case Manager</t>
   </si>
   <si>
@@ -730,12 +928,27 @@
     <t>Washington, Washington DC</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/843ba5f820a54344a082c228de287741-chief-development-officer-covenant-house-greater-washington-washington</t>
   </si>
   <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>VisArts</t>
+  </si>
+  <si>
+    <t>Rockville, Maryland</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/288411d1b2584a53b679cedeff665014-chief-operating-officer-visarts-rockville</t>
+  </si>
+  <si>
     <t>Child Trauma Counselor CTRT</t>
   </si>
   <si>
@@ -829,15 +1042,111 @@
     <t>https://www.idealist.org/en/nonprofit-job/8c6748da06534f4884d64e614d50523a-communications-and-events-manager-west-end-house-boston</t>
   </si>
   <si>
+    <t>Communications Director</t>
+  </si>
+  <si>
+    <t>Black LGBTQIA Migrant Project (BLMP)</t>
+  </si>
+  <si>
+    <t>USD 114500.00 - 114500.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Lgbtq, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5a2873bd55343daad2753533dcc75e8-communications-director-black-lgbtqia-migrant-project-blmp-oakland</t>
+  </si>
+  <si>
+    <t>Community Security Advisor</t>
+  </si>
+  <si>
+    <t>Jewish Federation Bay Area</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/734ca4d258594bfba896605ee83d8bee-community-security-advisor-jewish-federation-bay-area-san-francisco</t>
+  </si>
+  <si>
+    <t>Corporate Relations Engagement Officer</t>
+  </si>
+  <si>
+    <t>College Success Foundation</t>
+  </si>
+  <si>
+    <t>Bellevue, Washington</t>
+  </si>
+  <si>
+    <t>USD 49.00 - 73.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b42bbd615b3465e875f9e9aac76c7ad-corporate-relations-engagement-officer-college-success-foundation-bellevue</t>
+  </si>
+  <si>
+    <t>Corridor Program Managing Attorney</t>
+  </si>
+  <si>
+    <t>Dependency Advocacy Center</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 108000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16b978e6386644b1b3528e6b1a628a4b-corridor-program-managing-attorney-dependency-advocacy-center-san-jose</t>
+  </si>
+  <si>
+    <t>Country Finance Director</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation Society &amp; Miami University</t>
+  </si>
+  <si>
+    <t>Kampala, Central Region, UG</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0fd605b09c5a4835b7b10b4938763ecb-country-finance-director-wildlife-conservation-society-miami-university-kampala</t>
+  </si>
+  <si>
+    <t>Customer Service Coordinator</t>
+  </si>
+  <si>
+    <t>Sunflower Bakery</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disability, Education, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/46254e0124884fb6bf99c7acef2664b9-customer-service-coordinator-sunflower-bakery-rockville</t>
+  </si>
+  <si>
     <t>Deputy Director - Portfolio Management</t>
   </si>
   <si>
     <t>San Francisco Mayor’s Office of Housing and Community Development</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 170976.00 - 218218.00/year</t>
   </si>
   <si>
@@ -871,6 +1180,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/8fd694a097344249a8a2f97d695a6cc1-development-and-communications-coordinator-kids-for-the-bay-berkeley</t>
   </si>
   <si>
+    <t>Development and Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Concrete Jungle</t>
+  </si>
+  <si>
+    <t>East Point, Georgia</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c66611ba5e04793a00a936b7066b7f4-development-and-operations-coordinator-concrete-jungle-east-point</t>
+  </si>
+  <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>Yeshivat Maharat</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Religion Spirituality, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0aa4b72f7a82493c884ce0a215f59158-development-manager-yeshivat-maharat-bronx-county</t>
+  </si>
+  <si>
     <t>Development Manager, Grants &amp; Operations</t>
   </si>
   <si>
@@ -883,18 +1225,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/79dcc3a91a2442c3a39de4a12d9146b7-development-manager-grants-operations-studio-in-a-school-association-new-york</t>
   </si>
   <si>
+    <t>Development Manager, New York Chapter</t>
+  </si>
+  <si>
+    <t>Remote (Rochester, New York)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2bceefe6824d4269bf7cdc23dc92d91c-development-manager-new-york-chapter-parkinsons-foundation-rochester</t>
+  </si>
+  <si>
     <t>Development Operations Associate</t>
   </si>
   <si>
     <t>Reproductive Freedom for All</t>
   </si>
   <si>
-    <t>Washington, District of Columbia</t>
-  </si>
-  <si>
-    <t>USD 50000.00 - 58000.00/year</t>
-  </si>
-  <si>
     <t>Human Rights Civil Liberties, Policy, Reproductive Health Rights</t>
   </si>
   <si>
@@ -922,6 +1267,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/3e769b40fe424505adec65202830ef2c-digital-director-central-communications-new-america-washington</t>
   </si>
   <si>
+    <t>Digital Fundraising Campaign Specialist</t>
+  </si>
+  <si>
+    <t>The WNET Group</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/567375827f6441aeb655aba4584258a3-digital-fundraising-campaign-specialist-the-wnet-group-new-york</t>
+  </si>
+  <si>
     <t>Digital Marketing Coordinator</t>
   </si>
   <si>
@@ -955,12 +1312,27 @@
     <t>USD 100000.00 - 120000.00/year</t>
   </si>
   <si>
-    <t>Animals, Education, Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/14e15dd09a6245bdbbb4ab7d7096a1db-director-of-development-educated-choices-program-peachtree-corners</t>
   </si>
   <si>
+    <t>Director of Early Childhood Education Center</t>
+  </si>
+  <si>
+    <t>ECDO</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efd4b20004054d7dae2025bfad426782-director-of-early-childhood-education-center-ecdo-new-york</t>
+  </si>
+  <si>
     <t>Director of Finance</t>
   </si>
   <si>
@@ -982,12 +1354,48 @@
     <t>School of VISUAL ARTS</t>
   </si>
   <si>
-    <t>USD 60000.00 - 60000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/d0cbc26156ca477097f5ecdaf801a694-director-of-operations-school-of-visual-arts-new-york</t>
   </si>
   <si>
+    <t>Director, Climate Adaptation</t>
+  </si>
+  <si>
+    <t>Defenders of Wildlife</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 127000.00 - 143000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/93fc1a8939e847d297b7bea7a072eb57-director-climate-adaptation-defenders-of-wildlife-washington</t>
+  </si>
+  <si>
+    <t>Director, Conservation Technology</t>
+  </si>
+  <si>
+    <t>USD 143000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68b234149fe6486a938a8032f5521b70-director-conservation-technology-defenders-of-wildlife-washington</t>
+  </si>
+  <si>
+    <t>Director, Operations and Outreach - National Mall Gateway</t>
+  </si>
+  <si>
+    <t>Trust for the National Mall</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78a05fd04a044131ae69dc639387cae4-director-operations-and-outreach-national-mall-gateway-trust-for-the-national-mall-washington</t>
+  </si>
+  <si>
     <t>Director, Public Programs</t>
   </si>
   <si>
@@ -1021,9 +1429,6 @@
     <t>USD 22.00 - 25.00/hour</t>
   </si>
   <si>
-    <t>Children Youth, Education, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/75619facb9f746fb8a8487c452088e36-early-childhood-education-program-facilitator-smart-from-the-start-inc-washington</t>
   </si>
   <si>
@@ -1057,15 +1462,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/5bb53c7068c64b7dbeea64c1c4ece3d2-ejecutivo-telefonico-aldeas-infantiles-y-juveniles-sos-de-mexico-i-a-p-ciudad-de-mexico</t>
   </si>
   <si>
+    <t>Emergency Services Specialist - Bilingual</t>
+  </si>
+  <si>
+    <t>Bradley Angle</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 25.88 - 25.88/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e73f3059e074fab9425b61cad0f9f3f-emergency-services-specialist-bilingual-bradley-angle-portland</t>
+  </si>
+  <si>
     <t>Enterprise Sales Representative</t>
   </si>
   <si>
     <t>Rescuing Leftover Cuisine</t>
   </si>
   <si>
-    <t>New York, NY</t>
-  </si>
-  <si>
     <t>USD 100000.00 - 100000.00/year</t>
   </si>
   <si>
@@ -1099,6 +1519,51 @@
     <t>https://www.idealist.org/en/nonprofit-job/cbc42e35bac64589a6a81841dc847a1e-executive-director-artsconnection-new-york</t>
   </si>
   <si>
+    <t>Southern Delaware Therapeutic &amp; Recreational Horseback Riding, Inc.</t>
+  </si>
+  <si>
+    <t>Milton, Delaware</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Children Youth, Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42c91bfed2c94e08aa0e6510794b3bb2-executive-director-southern-delaware-therapeutic-recreational-horseback-riding-inc-milton</t>
+  </si>
+  <si>
+    <t>The Children's Network of Solano County</t>
+  </si>
+  <si>
+    <t>Fairfield, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5373430e3ba347dc982e1bc3e63d61ed-executive-director-the-childrens-network-of-solano-county-fairfield</t>
+  </si>
+  <si>
+    <t>Executive Director, Musizi University Foundation</t>
+  </si>
+  <si>
+    <t>Musizi University</t>
+  </si>
+  <si>
+    <t>USD 85000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Poverty, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f603961135974d90aa15367fb29e1067-executive-director-musizi-university-foundation-musizi-university-oakland</t>
+  </si>
+  <si>
     <t>Executive Facilitator + Nonprofit Collaboration Expert</t>
   </si>
   <si>
@@ -1144,6 +1609,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/fb27771740f74d2da68cace726d96e85-facilities-administrative-coordinator-the-james-irvine-foundation-san-francisco</t>
   </si>
   <si>
+    <t>Facility Associate</t>
+  </si>
+  <si>
+    <t>The Mountaineers</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.50/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/21912b86f221400184e1d7bf7edc888f-facility-associate-the-mountaineers-seattle</t>
+  </si>
+  <si>
+    <t>Foundation Associate</t>
+  </si>
+  <si>
+    <t>The Giving Back Fund</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da0825d10a6d4d6d89177b8b24c87b52-foundation-associate-the-giving-back-fund-boston</t>
+  </si>
+  <si>
     <t>Full-Time Compost Operator</t>
   </si>
   <si>
@@ -1177,9 +1675,6 @@
     <t>DC Bar Foundation</t>
   </si>
   <si>
-    <t>Washington, DC</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -1192,15 +1687,33 @@
     <t>Legal Aid Chicago</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 75000.00 - 85000.00/year</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/5a5fdb91b9064fc3851881c382c6e77b-grants-financial-manager-legal-aid-chicago-chicago</t>
   </si>
   <si>
+    <t>Head of Social &amp; Digital Brand for Global Compassion Coalition</t>
+  </si>
+  <si>
+    <t>Global Compassion Coalition</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0f63be060b9542b0bc353303d320a4e2-head-of-social-digital-brand-for-global-compassion-coalition-global-compassion-coalition-san-rafael</t>
+  </si>
+  <si>
+    <t>Human Trafficking Project Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4e6ffdc550cc4785af8610b25b09a103-human-trafficking-project-coordinator-life-span-chicago</t>
+  </si>
+  <si>
     <t>Immigration Attorney</t>
   </si>
   <si>
@@ -1210,12 +1723,48 @@
     <t>USD 90000.00 - 96000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Community Development, Economic Development</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/08ac2deddae0480dbe88fadd06982ccb-immigration-attorney-nmic-northern-manhattan-improvement-corporation-new-york</t>
   </si>
   <si>
+    <t>Intellectual and Developmental Disabilities Advocate</t>
+  </si>
+  <si>
+    <t>Quality Trust for Individuals with Disabilities</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Disability</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf276db763114698a51955db23cd7f90-intellectual-and-developmental-disabilities-advocate-quality-trust-for-individuals-with-disabilities-washington</t>
+  </si>
+  <si>
+    <t>Library Associate</t>
+  </si>
+  <si>
+    <t>The New York Society Library</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/450abf7de72b452994c4c27b66bb9bd1-library-associate-the-new-york-society-library-new-york</t>
+  </si>
+  <si>
+    <t>Major Gifts Officer</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2903cd1b9120400394a550292eda7383-major-gifts-officer-wildlife-conservation-society-miami-university-bronx-county</t>
+  </si>
+  <si>
     <t>Major Gifts Officer, East Region</t>
   </si>
   <si>
@@ -1243,6 +1792,30 @@
     <t>https://www.idealist.org/en/job/3136615153394196afd698a80824e608-managing-appeals-attorney-detained-adult-program-amica-center-for-immigrant-rights-amica-center-washington</t>
   </si>
   <si>
+    <t>MC2 Program Manager</t>
+  </si>
+  <si>
+    <t>AFL-CIO Working for America Institute</t>
+  </si>
+  <si>
+    <t>Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4077a6b729c4674a7e766de08da75d3-mc2-program-manager-afl-cio-working-for-america-institute-washington</t>
+  </si>
+  <si>
+    <t>Elba Hope Foundation</t>
+  </si>
+  <si>
+    <t>USD 5800.00 - 6250.00/month</t>
+  </si>
+  <si>
+    <t>Agriculture, Children Youth, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20202fc6b15c409a93d5169145c40708-operations-manager-elba-hope-foundation-new-york</t>
+  </si>
+  <si>
     <t>Part Time Arts Administrator - Education Program Assistant</t>
   </si>
   <si>
@@ -1267,9 +1840,6 @@
     <t>Darien, Connecticut</t>
   </si>
   <si>
-    <t>USD 25.00 - 25.00/hour</t>
-  </si>
-  <si>
     <t>Poverty, Volunteering</t>
   </si>
   <si>
@@ -1291,6 +1861,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/453ee67ee2654bebb1bb915d0b0f803f-part-time-community-organizer-arab-american-association-of-new-york-kings-county</t>
   </si>
   <si>
+    <t>Pathwaves Executive Director</t>
+  </si>
+  <si>
+    <t>Pathwaves WA</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3bd65070709045bba81fcadacb9e9eb4-pathwaves-executive-director-pathwaves-wa-seattle</t>
+  </si>
+  <si>
+    <t>Payroll Generalist</t>
+  </si>
+  <si>
+    <t>National Institute for Excellence in Teaching</t>
+  </si>
+  <si>
+    <t>Remote (Scottsdale, Arizona)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37b965df19424ee89c5cf008fc04437d-payroll-generalist-national-institute-for-excellence-in-teaching-scottsdale</t>
+  </si>
+  <si>
     <t>Peer Review Support Assistant</t>
   </si>
   <si>
@@ -1330,6 +1930,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/9845aa5e32b841109878186342feeada-professional-advancement-program-manager-prep-for-prep-new-york</t>
   </si>
   <si>
+    <t>Program Assistant</t>
+  </si>
+  <si>
+    <t>Argosy Foundation</t>
+  </si>
+  <si>
+    <t>Boulder, CO</t>
+  </si>
+  <si>
+    <t>USD 50000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Science Technology, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1131ec65deea4d4d97ad9b76b0d1d3f8-program-assistant-argosy-foundation-boulder</t>
+  </si>
+  <si>
     <t>Program Associate</t>
   </si>
   <si>
@@ -1345,6 +1963,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/f694e7050c7f4991b0f599b0d855c081-program-associate-amazon-conservation-association-washington</t>
   </si>
   <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/37a6ccde87ee4ad7b442abf4f386796b-program-associate-afl-cio-working-for-america-institute-washington</t>
+  </si>
+  <si>
+    <t>Program Associate, SF Diller Teen Fellows (Part-Time)</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/816d9b57f5004c2e8696e4db6d98bb03-program-associate-sf-diller-teen-fellows-part-time-jewish-federation-bay-area-san-francisco</t>
+  </si>
+  <si>
     <t>Program Coordinator</t>
   </si>
   <si>
@@ -1366,15 +2002,27 @@
     <t>https://www.idealist.org/en/job/a500e162867e49c69263a2ed885df7f1-program-director-careers-in-nonprofits-inc-college-point</t>
   </si>
   <si>
+    <t>Program Evaluator</t>
+  </si>
+  <si>
+    <t>Plan A Health, Inc</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Reproductive Health Rights, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5152e59bddba4403988525e924f75f8c-program-evaluator-plan-a-health-inc-louise</t>
+  </si>
+  <si>
     <t>Public Safety Manager</t>
   </si>
   <si>
     <t>Downtown Brooklyn Partnership</t>
   </si>
   <si>
-    <t>USD 70000.00 - 80000.00/year</t>
-  </si>
-  <si>
     <t>Community Development, Urban Areas, Crime Safety</t>
   </si>
   <si>
@@ -1447,12 +2095,30 @@
     <t>USD 95000.00 - 110000.00/year</t>
   </si>
   <si>
-    <t>Job Workplace</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/job/a175520e662e4042a58410f9248bafb9-senior-associate-nonprofit-professionals-advisory-group-beaverton</t>
   </si>
   <si>
+    <t>Senior Development Officer</t>
+  </si>
+  <si>
+    <t>Vision To Learn</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c02934659cf740eabe62b5cb6eaffb46-senior-development-officer-vision-to-learn-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Director, Data Operations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4395ee9bb0764817a87c9b1620b5a51e-senior-director-data-operations-parkinsons-foundation-miami</t>
+  </si>
+  <si>
     <t>Senior Director, Global Accounting</t>
   </si>
   <si>
@@ -1522,6 +2188,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/6b76f2553ac548b5b9f01dfb33db426a-senior-manager-payroll-operations-accounting-partners-for-rural-impact-berea</t>
   </si>
   <si>
+    <t>Senior Program Manager of Strategic Partnerships</t>
+  </si>
+  <si>
+    <t>Literacy Partners, Inc.</t>
+  </si>
+  <si>
+    <t>Las Vegas, Nevada</t>
+  </si>
+  <si>
+    <t>USD 71250.00 - 74250.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9112bd51276840328ad11dfe1512eef3-senior-program-manager-of-strategic-partnerships-literacy-partners-inc-las-vegas</t>
+  </si>
+  <si>
+    <t>San Diego, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2db46001eef1449fa5336a8ab7878734-senior-program-manager-of-strategic-partnerships-literacy-partners-inc-san-diego</t>
+  </si>
+  <si>
     <t>Senior Project Manager of Shelter Systems and Rapid Resolution</t>
   </si>
   <si>
@@ -1543,9 +2233,6 @@
     <t>Green City Force</t>
   </si>
   <si>
-    <t>USD 50000.00 - 55000.00/year</t>
-  </si>
-  <si>
     <t>Agriculture, Energy, Entrepreneurship</t>
   </si>
   <si>
@@ -1570,6 +2257,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/292412b4012f4c108c64488d4d4a61eb-service-enriched-housing-super-hero-community-housing-resource-partners-inc-houston</t>
   </si>
   <si>
+    <t>Shelter Family Advocate - Bilingual</t>
+  </si>
+  <si>
+    <t>USD 29.50 - 29.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/abb719490cfd49019241241b48f23ee8-shelter-family-advocate-bilingual-bradley-angle-portland</t>
+  </si>
+  <si>
     <t>Speech Therapist</t>
   </si>
   <si>
@@ -1585,6 +2281,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/68986ca7e89f4ea48f6dfb568517024f-speech-therapist-youth-villages-memphis</t>
   </si>
   <si>
+    <t>Sr. Social Worker</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e6ffddfd6d947a4b40b258027be9ec6-sr-social-worker-central-union-mission-washington</t>
+  </si>
+  <si>
     <t>Staff Accountant</t>
   </si>
   <si>
@@ -1600,6 +2305,48 @@
     <t>https://www.idealist.org/en/nonprofit-job/c8491f1797d2471c8b439ca4afd7344d-staff-accountant-american-association-for-justice-washington</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/07c3fa7d79834552af98d5bf68a0b19d-staff-accountant-national-institute-for-excellence-in-teaching-scottsdale</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Disability Law Center</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 70500.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f05d2c2985804da7b8e6b6327ec3d460-staff-attorney-disability-law-center-boston</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/143bd81c58a5495d99ab8c051192e884-staff-attorney-dependency-advocacy-center-san-jose</t>
+  </si>
+  <si>
+    <t>Save the Sound, Inc.</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b193e6d081ba4d10936a4fbb206e858e-staff-attorney-save-the-sound-inc-new-haven</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Pro Bono Coordinator</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a012764105aa42bcb12ddb0fac9358dd-staff-attorney-pro-bono-coordinator-canal-alliance-marin-california-san-rafael</t>
+  </si>
+  <si>
     <t>Suicide Prevention Services Manager</t>
   </si>
   <si>
@@ -1633,9 +2380,6 @@
     <t>San Buenaventur, san buenaventura, BO</t>
   </si>
   <si>
-    <t>Animals, Climate Change, Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/f11d5d3271094b7495061ad396c05023-veterinario-principal-trabajar-con-la-fauna-silvestre-en-la-selva-boliviana-comunidad-inti-wara-yassi-ciwy-san-buenaventur</t>
   </si>
   <si>
@@ -1649,6 +2393,12 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/job/2e383ed1b9634c5aa1353fc96bf6562b-vice-president-of-people-culture-future-now-hartford</t>
+  </si>
+  <si>
+    <t>Virtual and Learning Technology Services (VLTS) Support Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8c0d9554f4f240e0ab3b5275b809d748-virtual-and-learning-technology-services-vlts-support-manager-national-institute-for-excellence-in-teaching-scottsdale</t>
   </si>
   <si>
     <t>Workforce Cafe Coordinator, Workforce Development</t>
@@ -2801,7 +3551,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2986,79 +3736,79 @@
         <v>195</v>
       </c>
       <c r="C8" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="D8" t="s">
         <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D9" t="s">
         <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D10" t="s">
         <v>158</v>
       </c>
       <c r="E10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="D11" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
         <v>214</v>
@@ -3098,789 +3848,789 @@
         <v>223</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="D13" t="s">
         <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>185</v>
+        <v>225</v>
       </c>
       <c r="F13" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B14" t="s">
-        <v>183</v>
+        <v>229</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="D14" t="s">
         <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="F14" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B15" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C15" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
         <v>158</v>
       </c>
       <c r="E15" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F15" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B16" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E16" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F16" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="D17" t="s">
         <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="F17" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B18" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C18" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E18" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F18" t="s">
-        <v>167</v>
+        <v>256</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B19" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C19" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D19" t="s">
         <v>158</v>
       </c>
       <c r="E19" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F19" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B20" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="C20" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="D20" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E20" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B21" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D21" t="s">
         <v>158</v>
       </c>
       <c r="E21" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F21" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B22" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="C22" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
         <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="F22" t="s">
-        <v>269</v>
+        <v>209</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B23" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C23" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E23" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="F23" t="s">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B24" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C24" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E24" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="F24" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="C25" t="s">
-        <v>281</v>
+        <v>202</v>
       </c>
       <c r="D25" t="s">
         <v>158</v>
       </c>
       <c r="E25" t="s">
-        <v>282</v>
+        <v>203</v>
       </c>
       <c r="F25" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s">
-        <v>286</v>
+        <v>201</v>
       </c>
       <c r="C26" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="D26" t="s">
         <v>158</v>
       </c>
       <c r="E26" t="s">
-        <v>287</v>
+        <v>203</v>
       </c>
       <c r="F26" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C27" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D27" t="s">
         <v>158</v>
       </c>
       <c r="E27" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F27" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C28" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="D28" t="s">
         <v>158</v>
       </c>
       <c r="E28" t="s">
-        <v>292</v>
+        <v>209</v>
       </c>
       <c r="F28" t="s">
-        <v>293</v>
+        <v>209</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B29" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C29" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D29" t="s">
         <v>158</v>
       </c>
       <c r="E29" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="F29" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B30" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C30" t="s">
-        <v>304</v>
+        <v>170</v>
       </c>
       <c r="D30" t="s">
         <v>158</v>
       </c>
       <c r="E30" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="F30" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B31" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C31" t="s">
-        <v>170</v>
+        <v>318</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E31" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="F31" t="s">
-        <v>238</v>
+        <v>167</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B32" t="s">
-        <v>189</v>
+        <v>322</v>
       </c>
       <c r="C32" t="s">
-        <v>190</v>
+        <v>323</v>
       </c>
       <c r="D32" t="s">
         <v>158</v>
       </c>
       <c r="E32" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="F32" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B33" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C33" t="s">
-        <v>190</v>
+        <v>328</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="F33" t="s">
-        <v>318</v>
+        <v>167</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="C34" t="s">
-        <v>170</v>
+        <v>333</v>
       </c>
       <c r="D34" t="s">
         <v>158</v>
       </c>
       <c r="E34" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="F34" t="s">
-        <v>203</v>
+        <v>335</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B35" t="s">
-        <v>286</v>
+        <v>338</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="F35" t="s">
-        <v>269</v>
+        <v>340</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C36" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="D36" t="s">
         <v>158</v>
       </c>
       <c r="E36" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="F36" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="C37" t="s">
-        <v>291</v>
+        <v>349</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E37" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="F37" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="B38" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C38" t="s">
-        <v>190</v>
+        <v>355</v>
       </c>
       <c r="D38" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="E38" t="s">
-        <v>263</v>
+        <v>356</v>
       </c>
       <c r="F38" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C39" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="D39" t="s">
         <v>158</v>
       </c>
       <c r="E39" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="F39" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C40" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="D40" t="s">
         <v>158</v>
       </c>
       <c r="E40" t="s">
-        <v>350</v>
+        <v>209</v>
       </c>
       <c r="F40" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="C41" t="s">
-        <v>190</v>
+        <v>307</v>
       </c>
       <c r="D41" t="s">
         <v>158</v>
       </c>
       <c r="E41" t="s">
-        <v>202</v>
+        <v>372</v>
       </c>
       <c r="F41" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C42" t="s">
-        <v>170</v>
+        <v>349</v>
       </c>
       <c r="D42" t="s">
         <v>158</v>
       </c>
       <c r="E42" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="F42" t="s">
-        <v>269</v>
+        <v>378</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="D43" t="s">
-        <v>364</v>
+        <v>158</v>
       </c>
       <c r="E43" t="s">
-        <v>238</v>
+        <v>377</v>
       </c>
       <c r="F43" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B44" t="s">
-        <v>321</v>
+        <v>383</v>
       </c>
       <c r="C44" t="s">
-        <v>170</v>
+        <v>384</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E44" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="F44" t="s">
-        <v>203</v>
+        <v>386</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="C45" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="D45" t="s">
         <v>158</v>
       </c>
       <c r="E45" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="F45" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="B46" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="D46" t="s">
         <v>158</v>
       </c>
       <c r="E46" t="s">
-        <v>258</v>
+        <v>396</v>
       </c>
       <c r="F46" t="s">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>379</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="C47" t="s">
         <v>170</v>
@@ -3889,251 +4639,251 @@
         <v>158</v>
       </c>
       <c r="E47" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="F47" t="s">
-        <v>383</v>
+        <v>340</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s">
-        <v>386</v>
+        <v>183</v>
       </c>
       <c r="C48" t="s">
-        <v>387</v>
+        <v>404</v>
       </c>
       <c r="D48" t="s">
         <v>158</v>
       </c>
       <c r="E48" t="s">
-        <v>388</v>
+        <v>298</v>
       </c>
       <c r="F48" t="s">
-        <v>238</v>
+        <v>186</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="B49" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C49" t="s">
-        <v>392</v>
+        <v>254</v>
       </c>
       <c r="D49" t="s">
         <v>158</v>
       </c>
       <c r="E49" t="s">
-        <v>393</v>
+        <v>255</v>
       </c>
       <c r="F49" t="s">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="B50" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>349</v>
       </c>
       <c r="D50" t="s">
         <v>158</v>
       </c>
       <c r="E50" t="s">
-        <v>397</v>
+        <v>255</v>
       </c>
       <c r="F50" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B51" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C51" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="D51" t="s">
         <v>158</v>
       </c>
       <c r="E51" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="F51" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B52" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C52" t="s">
-        <v>291</v>
+        <v>170</v>
       </c>
       <c r="D52" t="s">
         <v>158</v>
       </c>
       <c r="E52" t="s">
-        <v>407</v>
+        <v>298</v>
       </c>
       <c r="F52" t="s">
-        <v>238</v>
+        <v>419</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C53" t="s">
-        <v>291</v>
+        <v>423</v>
       </c>
       <c r="D53" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E53" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="F53" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C54" t="s">
-        <v>416</v>
+        <v>170</v>
       </c>
       <c r="D54" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E54" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="F54" t="s">
-        <v>418</v>
+        <v>209</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s">
-        <v>421</v>
+        <v>213</v>
       </c>
       <c r="C55" t="s">
-        <v>422</v>
+        <v>184</v>
       </c>
       <c r="D55" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E55" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="F55" t="s">
-        <v>238</v>
+        <v>368</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="B56" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C56" t="s">
-        <v>201</v>
+        <v>435</v>
       </c>
       <c r="D56" t="s">
         <v>158</v>
       </c>
       <c r="E56" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="F56" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B57" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C57" t="s">
-        <v>291</v>
+        <v>184</v>
       </c>
       <c r="D57" t="s">
         <v>158</v>
       </c>
       <c r="E57" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="F57" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B58" t="s">
-        <v>309</v>
+        <v>445</v>
       </c>
       <c r="C58" t="s">
         <v>170</v>
@@ -4142,481 +4892,481 @@
         <v>158</v>
       </c>
       <c r="E58" t="s">
-        <v>436</v>
+        <v>261</v>
       </c>
       <c r="F58" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C59" t="s">
-        <v>291</v>
+        <v>449</v>
       </c>
       <c r="D59" t="s">
         <v>158</v>
       </c>
       <c r="E59" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="F59" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s">
-        <v>333</v>
+        <v>448</v>
       </c>
       <c r="C60" t="s">
-        <v>291</v>
+        <v>449</v>
       </c>
       <c r="D60" t="s">
         <v>158</v>
       </c>
       <c r="E60" t="s">
-        <v>232</v>
+        <v>454</v>
       </c>
       <c r="F60" t="s">
-        <v>335</v>
+        <v>451</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C61" t="s">
-        <v>447</v>
+        <v>254</v>
       </c>
       <c r="D61" t="s">
         <v>158</v>
       </c>
       <c r="E61" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="F61" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="B62" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="C62" t="s">
-        <v>422</v>
+        <v>170</v>
       </c>
       <c r="D62" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E62" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="F62" t="s">
-        <v>453</v>
+        <v>340</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="C63" t="s">
-        <v>457</v>
+        <v>170</v>
       </c>
       <c r="D63" t="s">
         <v>158</v>
       </c>
       <c r="E63" t="s">
-        <v>238</v>
+        <v>465</v>
       </c>
       <c r="F63" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="C64" t="s">
-        <v>462</v>
+        <v>254</v>
       </c>
       <c r="D64" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E64" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="F64" t="s">
-        <v>464</v>
+        <v>221</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B65" t="s">
-        <v>176</v>
+        <v>473</v>
       </c>
       <c r="C65" t="s">
-        <v>467</v>
+        <v>184</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E65" t="s">
-        <v>468</v>
+        <v>334</v>
       </c>
       <c r="F65" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s">
-        <v>309</v>
+        <v>477</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>478</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E66" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="F66" t="s">
-        <v>238</v>
+        <v>480</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="C67" t="s">
-        <v>190</v>
+        <v>484</v>
       </c>
       <c r="D67" t="s">
         <v>158</v>
       </c>
       <c r="E67" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="F67" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C68" t="s">
-        <v>190</v>
+        <v>435</v>
       </c>
       <c r="D68" t="s">
         <v>158</v>
       </c>
       <c r="E68" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F68" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B69" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="C69" t="s">
-        <v>422</v>
+        <v>184</v>
       </c>
       <c r="D69" t="s">
         <v>158</v>
       </c>
       <c r="E69" t="s">
-        <v>486</v>
+        <v>231</v>
       </c>
       <c r="F69" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="C70" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="D70" t="s">
         <v>158</v>
       </c>
       <c r="E70" t="s">
-        <v>407</v>
+        <v>499</v>
       </c>
       <c r="F70" t="s">
-        <v>491</v>
+        <v>340</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C71" t="s">
-        <v>190</v>
+        <v>502</v>
       </c>
       <c r="D71" t="s">
         <v>158</v>
       </c>
       <c r="E71" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F71" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B72" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="C72" t="s">
-        <v>190</v>
+        <v>507</v>
       </c>
       <c r="D72" t="s">
         <v>158</v>
       </c>
       <c r="E72" t="s">
-        <v>238</v>
+        <v>508</v>
       </c>
       <c r="F72" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B73" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="C73" t="s">
-        <v>504</v>
+        <v>184</v>
       </c>
       <c r="D73" t="s">
         <v>158</v>
       </c>
       <c r="E73" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F73" t="s">
-        <v>275</v>
+        <v>514</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B74" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C74" t="s">
-        <v>422</v>
+        <v>518</v>
       </c>
       <c r="D74" t="s">
-        <v>158</v>
+        <v>519</v>
       </c>
       <c r="E74" t="s">
-        <v>509</v>
+        <v>209</v>
       </c>
       <c r="F74" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>511</v>
+        <v>521</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="B75" t="s">
-        <v>513</v>
+        <v>445</v>
       </c>
       <c r="C75" t="s">
-        <v>514</v>
+        <v>170</v>
       </c>
       <c r="D75" t="s">
         <v>165</v>
       </c>
       <c r="E75" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="F75" t="s">
-        <v>516</v>
+        <v>232</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B76" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C76" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="D76" t="s">
         <v>158</v>
       </c>
       <c r="E76" t="s">
-        <v>238</v>
+        <v>528</v>
       </c>
       <c r="F76" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B77" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="C77" t="s">
-        <v>291</v>
+        <v>533</v>
       </c>
       <c r="D77" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E77" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="F77" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="B78" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C78" t="s">
-        <v>530</v>
+        <v>184</v>
       </c>
       <c r="D78" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E78" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="F78" t="s">
-        <v>464</v>
+        <v>540</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="B79" t="s">
-        <v>396</v>
+        <v>543</v>
       </c>
       <c r="C79" t="s">
         <v>170</v>
@@ -4625,105 +5375,1439 @@
         <v>158</v>
       </c>
       <c r="E79" t="s">
-        <v>534</v>
+        <v>329</v>
       </c>
       <c r="F79" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>547</v>
       </c>
       <c r="C80" t="s">
-        <v>538</v>
+        <v>170</v>
       </c>
       <c r="D80" t="s">
         <v>158</v>
       </c>
       <c r="E80" t="s">
-        <v>468</v>
+        <v>548</v>
       </c>
       <c r="F80" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="C81" t="s">
-        <v>190</v>
+        <v>449</v>
       </c>
       <c r="D81" t="s">
         <v>158</v>
       </c>
       <c r="E81" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
       <c r="F81" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="C82" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="D82" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E82" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="F82" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="B83" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="C83" t="s">
-        <v>552</v>
+        <v>184</v>
       </c>
       <c r="D83" t="s">
+        <v>519</v>
+      </c>
+      <c r="E83" t="s">
+        <v>561</v>
+      </c>
+      <c r="F83" t="s">
+        <v>562</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>564</v>
+      </c>
+      <c r="B84" t="s">
+        <v>270</v>
+      </c>
+      <c r="C84" t="s">
+        <v>271</v>
+      </c>
+      <c r="D84" t="s">
+        <v>158</v>
+      </c>
+      <c r="E84" t="s">
+        <v>272</v>
+      </c>
+      <c r="F84" t="s">
+        <v>273</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>566</v>
+      </c>
+      <c r="B85" t="s">
+        <v>567</v>
+      </c>
+      <c r="C85" t="s">
+        <v>170</v>
+      </c>
+      <c r="D85" t="s">
+        <v>158</v>
+      </c>
+      <c r="E85" t="s">
+        <v>568</v>
+      </c>
+      <c r="F85" t="s">
+        <v>192</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>570</v>
+      </c>
+      <c r="B86" t="s">
+        <v>571</v>
+      </c>
+      <c r="C86" t="s">
+        <v>572</v>
+      </c>
+      <c r="D86" t="s">
+        <v>158</v>
+      </c>
+      <c r="E86" t="s">
+        <v>573</v>
+      </c>
+      <c r="F86" t="s">
+        <v>574</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>576</v>
+      </c>
+      <c r="B87" t="s">
+        <v>577</v>
+      </c>
+      <c r="C87" t="s">
+        <v>170</v>
+      </c>
+      <c r="D87" t="s">
         <v>165</v>
       </c>
-      <c r="E83" t="s">
-        <v>214</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E87" t="s">
+        <v>578</v>
+      </c>
+      <c r="F87" t="s">
+        <v>209</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>580</v>
+      </c>
+      <c r="B88" t="s">
+        <v>366</v>
+      </c>
+      <c r="C88" t="s">
+        <v>196</v>
+      </c>
+      <c r="D88" t="s">
+        <v>158</v>
+      </c>
+      <c r="E88" t="s">
+        <v>581</v>
+      </c>
+      <c r="F88" t="s">
+        <v>335</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>583</v>
+      </c>
+      <c r="B89" t="s">
+        <v>584</v>
+      </c>
+      <c r="C89" t="s">
+        <v>230</v>
+      </c>
+      <c r="D89" t="s">
+        <v>158</v>
+      </c>
+      <c r="E89" t="s">
+        <v>585</v>
+      </c>
+      <c r="F89" t="s">
+        <v>586</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>588</v>
+      </c>
+      <c r="B90" t="s">
+        <v>589</v>
+      </c>
+      <c r="C90" t="s">
+        <v>254</v>
+      </c>
+      <c r="D90" t="s">
+        <v>158</v>
+      </c>
+      <c r="E90" t="s">
+        <v>590</v>
+      </c>
+      <c r="F90" t="s">
+        <v>209</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>592</v>
+      </c>
+      <c r="B91" t="s">
+        <v>593</v>
+      </c>
+      <c r="C91" t="s">
+        <v>254</v>
+      </c>
+      <c r="D91" t="s">
+        <v>158</v>
+      </c>
+      <c r="E91" t="s">
+        <v>585</v>
+      </c>
+      <c r="F91" t="s">
+        <v>594</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>61</v>
+      </c>
+      <c r="B92" t="s">
+        <v>596</v>
+      </c>
+      <c r="C92" t="s">
+        <v>184</v>
+      </c>
+      <c r="D92" t="s">
+        <v>519</v>
+      </c>
+      <c r="E92" t="s">
+        <v>597</v>
+      </c>
+      <c r="F92" t="s">
+        <v>598</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>600</v>
+      </c>
+      <c r="B93" t="s">
+        <v>601</v>
+      </c>
+      <c r="C93" t="s">
+        <v>254</v>
+      </c>
+      <c r="D93" t="s">
+        <v>165</v>
+      </c>
+      <c r="E93" t="s">
+        <v>602</v>
+      </c>
+      <c r="F93" t="s">
+        <v>603</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>605</v>
+      </c>
+      <c r="B94" t="s">
+        <v>606</v>
+      </c>
+      <c r="C94" t="s">
+        <v>607</v>
+      </c>
+      <c r="D94" t="s">
+        <v>165</v>
+      </c>
+      <c r="E94" t="s">
+        <v>372</v>
+      </c>
+      <c r="F94" t="s">
+        <v>608</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>610</v>
+      </c>
+      <c r="B95" t="s">
+        <v>611</v>
+      </c>
+      <c r="C95" t="s">
+        <v>612</v>
+      </c>
+      <c r="D95" t="s">
+        <v>165</v>
+      </c>
+      <c r="E95" t="s">
+        <v>613</v>
+      </c>
+      <c r="F95" t="s">
+        <v>209</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>615</v>
+      </c>
+      <c r="B96" t="s">
+        <v>616</v>
+      </c>
+      <c r="C96" t="s">
+        <v>617</v>
+      </c>
+      <c r="D96" t="s">
+        <v>158</v>
+      </c>
+      <c r="E96" t="s">
+        <v>618</v>
+      </c>
+      <c r="F96" t="s">
+        <v>619</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>621</v>
+      </c>
+      <c r="B97" t="s">
+        <v>622</v>
+      </c>
+      <c r="C97" t="s">
+        <v>623</v>
+      </c>
+      <c r="D97" t="s">
+        <v>158</v>
+      </c>
+      <c r="E97" t="s">
+        <v>209</v>
+      </c>
+      <c r="F97" t="s">
+        <v>232</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>625</v>
+      </c>
+      <c r="B98" t="s">
+        <v>626</v>
+      </c>
+      <c r="C98" t="s">
+        <v>230</v>
+      </c>
+      <c r="D98" t="s">
+        <v>158</v>
+      </c>
+      <c r="E98" t="s">
+        <v>627</v>
+      </c>
+      <c r="F98" t="s">
+        <v>628</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>630</v>
+      </c>
+      <c r="B99" t="s">
+        <v>631</v>
+      </c>
+      <c r="C99" t="s">
+        <v>254</v>
+      </c>
+      <c r="D99" t="s">
+        <v>158</v>
+      </c>
+      <c r="E99" t="s">
+        <v>632</v>
+      </c>
+      <c r="F99" t="s">
+        <v>633</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>635</v>
+      </c>
+      <c r="B100" t="s">
+        <v>428</v>
+      </c>
+      <c r="C100" t="s">
+        <v>170</v>
+      </c>
+      <c r="D100" t="s">
+        <v>158</v>
+      </c>
+      <c r="E100" t="s">
+        <v>636</v>
+      </c>
+      <c r="F100" t="s">
+        <v>209</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>638</v>
+      </c>
+      <c r="B101" t="s">
+        <v>639</v>
+      </c>
+      <c r="C101" t="s">
+        <v>640</v>
+      </c>
+      <c r="D101" t="s">
+        <v>158</v>
+      </c>
+      <c r="E101" t="s">
+        <v>641</v>
+      </c>
+      <c r="F101" t="s">
+        <v>642</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>644</v>
+      </c>
+      <c r="B102" t="s">
+        <v>645</v>
+      </c>
+      <c r="C102" t="s">
+        <v>254</v>
+      </c>
+      <c r="D102" t="s">
+        <v>158</v>
+      </c>
+      <c r="E102" t="s">
+        <v>646</v>
+      </c>
+      <c r="F102" t="s">
+        <v>647</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>644</v>
+      </c>
+      <c r="B103" t="s">
+        <v>593</v>
+      </c>
+      <c r="C103" t="s">
+        <v>254</v>
+      </c>
+      <c r="D103" t="s">
+        <v>158</v>
+      </c>
+      <c r="E103" t="s">
+        <v>649</v>
+      </c>
+      <c r="F103" t="s">
+        <v>594</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>651</v>
+      </c>
+      <c r="B104" t="s">
+        <v>348</v>
+      </c>
+      <c r="C104" t="s">
+        <v>349</v>
+      </c>
+      <c r="D104" t="s">
+        <v>165</v>
+      </c>
+      <c r="E104" t="s">
+        <v>652</v>
+      </c>
+      <c r="F104" t="s">
+        <v>653</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>655</v>
+      </c>
+      <c r="B105" t="s">
+        <v>469</v>
+      </c>
+      <c r="C105" t="s">
+        <v>254</v>
+      </c>
+      <c r="D105" t="s">
+        <v>158</v>
+      </c>
+      <c r="E105" t="s">
+        <v>298</v>
+      </c>
+      <c r="F105" t="s">
+        <v>221</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>657</v>
+      </c>
+      <c r="B106" t="s">
+        <v>658</v>
+      </c>
+      <c r="C106" t="s">
+        <v>659</v>
+      </c>
+      <c r="D106" t="s">
+        <v>158</v>
+      </c>
+      <c r="E106" t="s">
+        <v>660</v>
+      </c>
+      <c r="F106" t="s">
+        <v>209</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>662</v>
+      </c>
+      <c r="B107" t="s">
+        <v>663</v>
+      </c>
+      <c r="C107" t="s">
+        <v>184</v>
+      </c>
+      <c r="D107" t="s">
+        <v>158</v>
+      </c>
+      <c r="E107" t="s">
+        <v>664</v>
+      </c>
+      <c r="F107" t="s">
+        <v>665</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>667</v>
+      </c>
+      <c r="B108" t="s">
+        <v>668</v>
+      </c>
+      <c r="C108" t="s">
+        <v>612</v>
+      </c>
+      <c r="D108" t="s">
+        <v>158</v>
+      </c>
+      <c r="E108" t="s">
+        <v>185</v>
+      </c>
+      <c r="F108" t="s">
+        <v>669</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>671</v>
+      </c>
+      <c r="B109" t="s">
+        <v>672</v>
+      </c>
+      <c r="C109" t="s">
+        <v>673</v>
+      </c>
+      <c r="D109" t="s">
+        <v>158</v>
+      </c>
+      <c r="E109" t="s">
+        <v>209</v>
+      </c>
+      <c r="F109" t="s">
+        <v>674</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>676</v>
+      </c>
+      <c r="B110" t="s">
+        <v>677</v>
+      </c>
+      <c r="C110" t="s">
+        <v>678</v>
+      </c>
+      <c r="D110" t="s">
+        <v>158</v>
+      </c>
+      <c r="E110" t="s">
+        <v>679</v>
+      </c>
+      <c r="F110" t="s">
+        <v>680</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>682</v>
+      </c>
+      <c r="B111" t="s">
+        <v>176</v>
+      </c>
+      <c r="C111" t="s">
+        <v>683</v>
+      </c>
+      <c r="D111" t="s">
+        <v>158</v>
+      </c>
+      <c r="E111" t="s">
+        <v>684</v>
+      </c>
+      <c r="F111" t="s">
+        <v>685</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>687</v>
+      </c>
+      <c r="B112" t="s">
+        <v>428</v>
+      </c>
+      <c r="C112" t="s">
+        <v>170</v>
+      </c>
+      <c r="D112" t="s">
+        <v>171</v>
+      </c>
+      <c r="E112" t="s">
+        <v>688</v>
+      </c>
+      <c r="F112" t="s">
+        <v>209</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>690</v>
+      </c>
+      <c r="B113" t="s">
+        <v>691</v>
+      </c>
+      <c r="C113" t="s">
+        <v>184</v>
+      </c>
+      <c r="D113" t="s">
+        <v>158</v>
+      </c>
+      <c r="E113" t="s">
+        <v>692</v>
+      </c>
+      <c r="F113" t="s">
+        <v>594</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>694</v>
+      </c>
+      <c r="B114" t="s">
+        <v>695</v>
+      </c>
+      <c r="C114" t="s">
+        <v>184</v>
+      </c>
+      <c r="D114" t="s">
+        <v>158</v>
+      </c>
+      <c r="E114" t="s">
+        <v>696</v>
+      </c>
+      <c r="F114" t="s">
+        <v>697</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>699</v>
+      </c>
+      <c r="B115" t="s">
+        <v>183</v>
+      </c>
+      <c r="C115" t="s">
+        <v>184</v>
+      </c>
+      <c r="D115" t="s">
+        <v>158</v>
+      </c>
+      <c r="E115" t="s">
+        <v>461</v>
+      </c>
+      <c r="F115" t="s">
+        <v>209</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>701</v>
+      </c>
+      <c r="B116" t="s">
+        <v>702</v>
+      </c>
+      <c r="C116" t="s">
+        <v>184</v>
+      </c>
+      <c r="D116" t="s">
+        <v>158</v>
+      </c>
+      <c r="E116" t="s">
+        <v>703</v>
+      </c>
+      <c r="F116" t="s">
+        <v>704</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>706</v>
+      </c>
+      <c r="B117" t="s">
+        <v>707</v>
+      </c>
+      <c r="C117" t="s">
+        <v>612</v>
+      </c>
+      <c r="D117" t="s">
+        <v>158</v>
+      </c>
+      <c r="E117" t="s">
+        <v>708</v>
+      </c>
+      <c r="F117" t="s">
+        <v>709</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>711</v>
+      </c>
+      <c r="B118" t="s">
+        <v>712</v>
+      </c>
+      <c r="C118" t="s">
+        <v>230</v>
+      </c>
+      <c r="D118" t="s">
+        <v>158</v>
+      </c>
+      <c r="E118" t="s">
+        <v>590</v>
+      </c>
+      <c r="F118" t="s">
+        <v>713</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>715</v>
+      </c>
+      <c r="B119" t="s">
+        <v>716</v>
+      </c>
+      <c r="C119" t="s">
+        <v>184</v>
+      </c>
+      <c r="D119" t="s">
+        <v>158</v>
+      </c>
+      <c r="E119" t="s">
+        <v>717</v>
+      </c>
+      <c r="F119" t="s">
+        <v>718</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>720</v>
+      </c>
+      <c r="B120" t="s">
+        <v>721</v>
+      </c>
+      <c r="C120" t="s">
+        <v>184</v>
+      </c>
+      <c r="D120" t="s">
+        <v>158</v>
+      </c>
+      <c r="E120" t="s">
+        <v>209</v>
+      </c>
+      <c r="F120" t="s">
+        <v>722</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>724</v>
+      </c>
+      <c r="B121" t="s">
+        <v>725</v>
+      </c>
+      <c r="C121" t="s">
+        <v>726</v>
+      </c>
+      <c r="D121" t="s">
+        <v>158</v>
+      </c>
+      <c r="E121" t="s">
+        <v>727</v>
+      </c>
+      <c r="F121" t="s">
+        <v>728</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>724</v>
+      </c>
+      <c r="B122" t="s">
+        <v>725</v>
+      </c>
+      <c r="C122" t="s">
+        <v>730</v>
+      </c>
+      <c r="D122" t="s">
+        <v>158</v>
+      </c>
+      <c r="E122" t="s">
+        <v>727</v>
+      </c>
+      <c r="F122" t="s">
+        <v>728</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>732</v>
+      </c>
+      <c r="B123" t="s">
+        <v>733</v>
+      </c>
+      <c r="C123" t="s">
+        <v>734</v>
+      </c>
+      <c r="D123" t="s">
+        <v>158</v>
+      </c>
+      <c r="E123" t="s">
+        <v>735</v>
+      </c>
+      <c r="F123" t="s">
+        <v>378</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>737</v>
+      </c>
+      <c r="B124" t="s">
+        <v>738</v>
+      </c>
+      <c r="C124" t="s">
+        <v>612</v>
+      </c>
+      <c r="D124" t="s">
+        <v>158</v>
+      </c>
+      <c r="E124" t="s">
+        <v>391</v>
+      </c>
+      <c r="F124" t="s">
+        <v>739</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>741</v>
+      </c>
+      <c r="B125" t="s">
+        <v>742</v>
+      </c>
+      <c r="C125" t="s">
+        <v>743</v>
+      </c>
+      <c r="D125" t="s">
+        <v>165</v>
+      </c>
+      <c r="E125" t="s">
+        <v>744</v>
+      </c>
+      <c r="F125" t="s">
+        <v>745</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>747</v>
+      </c>
+      <c r="B126" t="s">
+        <v>483</v>
+      </c>
+      <c r="C126" t="s">
+        <v>484</v>
+      </c>
+      <c r="D126" t="s">
+        <v>158</v>
+      </c>
+      <c r="E126" t="s">
+        <v>748</v>
+      </c>
+      <c r="F126" t="s">
+        <v>486</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>750</v>
+      </c>
+      <c r="B127" t="s">
+        <v>751</v>
+      </c>
+      <c r="C127" t="s">
+        <v>752</v>
+      </c>
+      <c r="D127" t="s">
+        <v>158</v>
+      </c>
+      <c r="E127" t="s">
+        <v>209</v>
+      </c>
+      <c r="F127" t="s">
+        <v>753</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>755</v>
+      </c>
+      <c r="B128" t="s">
+        <v>265</v>
+      </c>
+      <c r="C128" t="s">
+        <v>254</v>
+      </c>
+      <c r="D128" t="s">
+        <v>158</v>
+      </c>
+      <c r="E128" t="s">
+        <v>756</v>
+      </c>
+      <c r="F128" t="s">
+        <v>209</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>758</v>
+      </c>
+      <c r="B129" t="s">
+        <v>759</v>
+      </c>
+      <c r="C129" t="s">
+        <v>254</v>
+      </c>
+      <c r="D129" t="s">
+        <v>158</v>
+      </c>
+      <c r="E129" t="s">
+        <v>760</v>
+      </c>
+      <c r="F129" t="s">
+        <v>761</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>758</v>
+      </c>
+      <c r="B130" t="s">
+        <v>622</v>
+      </c>
+      <c r="C130" t="s">
+        <v>623</v>
+      </c>
+      <c r="D130" t="s">
+        <v>158</v>
+      </c>
+      <c r="E130" t="s">
+        <v>209</v>
+      </c>
+      <c r="F130" t="s">
+        <v>232</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>764</v>
+      </c>
+      <c r="B131" t="s">
+        <v>765</v>
+      </c>
+      <c r="C131" t="s">
+        <v>766</v>
+      </c>
+      <c r="D131" t="s">
+        <v>158</v>
+      </c>
+      <c r="E131" t="s">
+        <v>767</v>
+      </c>
+      <c r="F131" t="s">
+        <v>768</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>764</v>
+      </c>
+      <c r="B132" t="s">
+        <v>360</v>
+      </c>
+      <c r="C132" t="s">
+        <v>361</v>
+      </c>
+      <c r="D132" t="s">
+        <v>158</v>
+      </c>
+      <c r="E132" t="s">
+        <v>770</v>
+      </c>
+      <c r="F132" t="s">
+        <v>363</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>764</v>
+      </c>
+      <c r="B133" t="s">
+        <v>772</v>
+      </c>
+      <c r="C133" t="s">
+        <v>208</v>
+      </c>
+      <c r="D133" t="s">
+        <v>158</v>
+      </c>
+      <c r="E133" t="s">
+        <v>773</v>
+      </c>
+      <c r="F133" t="s">
+        <v>335</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>775</v>
+      </c>
+      <c r="B134" t="s">
+        <v>189</v>
+      </c>
+      <c r="C134" t="s">
+        <v>190</v>
+      </c>
+      <c r="D134" t="s">
+        <v>158</v>
+      </c>
+      <c r="E134" t="s">
         <v>553</v>
       </c>
-      <c r="H83" s="2" t="s">
-        <v>554</v>
+      <c r="F134" t="s">
+        <v>192</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>777</v>
+      </c>
+      <c r="B135" t="s">
+        <v>778</v>
+      </c>
+      <c r="C135" t="s">
+        <v>779</v>
+      </c>
+      <c r="D135" t="s">
+        <v>158</v>
+      </c>
+      <c r="E135" t="s">
+        <v>780</v>
+      </c>
+      <c r="F135" t="s">
+        <v>680</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>782</v>
+      </c>
+      <c r="B136" t="s">
+        <v>567</v>
+      </c>
+      <c r="C136" t="s">
+        <v>170</v>
+      </c>
+      <c r="D136" t="s">
+        <v>158</v>
+      </c>
+      <c r="E136" t="s">
+        <v>783</v>
+      </c>
+      <c r="F136" t="s">
+        <v>784</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>786</v>
+      </c>
+      <c r="B137" t="s">
+        <v>176</v>
+      </c>
+      <c r="C137" t="s">
+        <v>787</v>
+      </c>
+      <c r="D137" t="s">
+        <v>158</v>
+      </c>
+      <c r="E137" t="s">
+        <v>684</v>
+      </c>
+      <c r="F137" t="s">
+        <v>451</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>789</v>
+      </c>
+      <c r="B138" t="s">
+        <v>790</v>
+      </c>
+      <c r="C138" t="s">
+        <v>184</v>
+      </c>
+      <c r="D138" t="s">
+        <v>158</v>
+      </c>
+      <c r="E138" t="s">
+        <v>791</v>
+      </c>
+      <c r="F138" t="s">
+        <v>209</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>793</v>
+      </c>
+      <c r="B139" t="s">
+        <v>622</v>
+      </c>
+      <c r="C139" t="s">
+        <v>623</v>
+      </c>
+      <c r="D139" t="s">
+        <v>158</v>
+      </c>
+      <c r="E139" t="s">
+        <v>209</v>
+      </c>
+      <c r="F139" t="s">
+        <v>232</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>795</v>
+      </c>
+      <c r="B140" t="s">
+        <v>796</v>
+      </c>
+      <c r="C140" t="s">
+        <v>254</v>
+      </c>
+      <c r="D140" t="s">
+        <v>171</v>
+      </c>
+      <c r="E140" t="s">
+        <v>797</v>
+      </c>
+      <c r="F140" t="s">
+        <v>798</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>800</v>
+      </c>
+      <c r="B141" t="s">
+        <v>801</v>
+      </c>
+      <c r="C141" t="s">
+        <v>802</v>
+      </c>
+      <c r="D141" t="s">
+        <v>165</v>
+      </c>
+      <c r="E141" t="s">
+        <v>243</v>
+      </c>
+      <c r="F141" t="s">
+        <v>803</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -4811,6 +6895,64 @@
     <hyperlink ref="H81" r:id="rId80"/>
     <hyperlink ref="H82" r:id="rId81"/>
     <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4860,25 +7002,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>555</v>
+        <v>805</v>
       </c>
       <c r="B2" t="s">
-        <v>556</v>
+        <v>806</v>
       </c>
       <c r="C2" t="s">
-        <v>557</v>
+        <v>807</v>
       </c>
       <c r="D2" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="F2" t="s">
-        <v>558</v>
+        <v>808</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>559</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
